--- a/reporting-site/public/reviews/task31/artifacts/Asia_Pacific_Welfare_Losses_Evidence_Register_2026.xlsx
+++ b/reporting-site/public/reviews/task31/artifacts/Asia_Pacific_Welfare_Losses_Evidence_Register_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Raymond\OneDrive\Desktop\ADB\Research\Task31\outputs\task31_welfare_review_20260804\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98A9294C-F97D-4A72-AF4A-EBC12801B8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{655C3B44-6E86-4335-BDDA-0D86EC3B92F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1380" windowWidth="4365" windowHeight="2820" xr2:uid="{01561435-22B8-497C-8B72-7BB004F02023}"/>
+    <workbookView xWindow="1380" yWindow="1380" windowWidth="4365" windowHeight="2820" xr2:uid="{A9AF3348-2B31-417F-88DA-41AE955719BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1603,7 +1603,7 @@
     <t>GDP per capita and between-country inequality</t>
   </si>
   <si>
-    <t>Warming increased population-weighted between-country inequality by about 25%; estimated GDP-per-capita losses were about 31% for India, 27% for Indonesia, and 12% for Bangladesh relative to a no-warming counterfactual</t>
+    <t>Warming increased population-weighted between-country inequality by about 25%; per-capita GDP was reduced 17%-31% at the poorest four deciles of the population-weighted country distribution, and the 18 countries with the lowest cumulative per-capita emissions had a median impact of about -27% relative to a no-warming counterfactual</t>
   </si>
   <si>
     <t>Detection-and-attribution climate simulations combined with nonlinear temperature-growth response</t>
@@ -1612,7 +1612,7 @@
     <t>Historical climate-attribution counterfactual</t>
   </si>
   <si>
-    <t>Depends on contested growth response and cumulative counterfactual; estimates are not household consumption losses</t>
+    <t>Depends on contested growth response and cumulative counterfactual; estimates are not household consumption losses. The previously recorded country figures (31% India, 27% Indonesia, 12% Bangladesh) are not supported by this paper: Indonesia and Bangladesh appear nowhere in its text, and the 31% and 27% figures are a decile range and a low-emitter median respectively, not country estimates (CONSTITUTION.md §2.7)</t>
   </si>
   <si>
     <t>Attribution model</t>
@@ -3988,7 +3988,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-EDA3-4C01-ADEC-BD2698985820}"/>
+              <c16:uniqueId val="{00000002-1C3C-4FF8-8145-7AF6CB0E78E5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4001,11 +4001,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="2034546112"/>
-        <c:axId val="2034542272"/>
+        <c:axId val="874096383"/>
+        <c:axId val="874103583"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2034546112"/>
+        <c:axId val="874096383"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4015,7 +4015,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2034542272"/>
+        <c:crossAx val="874103583"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4023,7 +4023,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2034542272"/>
+        <c:axId val="874103583"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4034,7 +4034,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="2034546112"/>
+        <c:crossAx val="874096383"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4102,7 +4102,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0176A5D-1424-8B34-0F69-3B7A6AEB2FDA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2D0E86-6C1E-4168-2739-89218884055C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4124,27 +4124,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5BCC931B-FE11-4829-A573-A6EE21D77119}" name="EvidenceTable" displayName="EvidenceTable" ref="A4:R56" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
-  <autoFilter ref="A4:R56" xr:uid="{5BCC931B-FE11-4829-A573-A6EE21D77119}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8619403-CE21-46A7-AF88-CE7029EC5606}" name="EvidenceTable" displayName="EvidenceTable" ref="A4:R56" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+  <autoFilter ref="A4:R56" xr:uid="{B8619403-CE21-46A7-AF88-CE7029EC5606}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{84421B4C-30D1-4E21-B8A6-98116C4550C8}" name="ID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{6DDA87EE-F657-481E-AE2F-C9854B1C4CAE}" name="Category" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{ACADB5C8-BF6E-4B4F-9EED-3F3FD61657DF}" name="Study" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{48A80B7C-B3CD-4137-A2D3-11120E65E08B}" name="Year" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{49951A0B-AD54-4564-808E-F3DDD00A1DEB}" name="Source" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{B0B3B937-E302-44C5-8373-F4E2E1D3D94A}" name="Geography" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{37B706B5-CED6-40CA-BB12-384A1E5935FA}" name="Subregion" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{6D4ABC17-949F-4305-A76A-3B257FE471BF}" name="Population" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{17024D4D-546C-431C-88E9-B300AD824651}" name="Shock" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{B11AABFC-10AA-4C58-BD96-FB780ED7117A}" name="Welfare Indicator" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{32EE9701-942D-47EA-B33A-39AF2A71E9A7}" name="Estimate" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{ED1D086C-F615-4ACE-841F-76C7542567AD}" name="Methodology" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{0E67F87D-5E89-4E05-BFB9-11CDF5E32F08}" name="Identification" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{AE0FB3BD-6673-4853-89F2-4A213616CC45}" name="Limitations" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{990E674D-360F-455B-9FE4-E886E6E9D117}" name="Confidence" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{6C33D149-9C54-4593-B60C-FD32A4EB2D4E}" name="Evidence Type" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{5A0F8D06-D7F9-4534-B693-7836434FD2DF}" name="URL" dataDxfId="0"/>
-    <tableColumn id="18" xr3:uid="{EEB7FDA4-10C1-487F-8802-EA71B695AAA2}" name="DOI" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{B3FA3C08-C0F6-422A-908C-0C744612F45F}" name="ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{AE0F1CC6-9119-40C1-807C-131133867D0A}" name="Category" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{A42FD296-1C89-42BA-8260-6886085B582B}" name="Study" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{84B47023-E2BA-44CE-B2BC-CBD694436B51}" name="Year" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{20921EFD-BC60-4888-B7C3-F2E68F797453}" name="Source" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{3B181883-EAE5-4C3E-99BF-9A60EC1814F0}" name="Geography" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{7FF065D4-0529-4BFC-8A6C-4BC630288B92}" name="Subregion" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{A79869C3-B49A-467F-8C35-B3EEC2BC8863}" name="Population" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{9996BE64-8891-4BBE-8472-8087358ACA93}" name="Shock" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{CEB475BB-92A1-40AF-B987-AA7D1F0832C7}" name="Welfare Indicator" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{2A0BB8F8-A434-467E-9812-5DD934E7C7E3}" name="Estimate" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{8CAA49FE-5966-4BC8-9353-4D0BECFAF297}" name="Methodology" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{415D5427-5FB6-4A7E-A058-23A7F09F292E}" name="Identification" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{7AF0A998-C35B-4423-AC46-1E7329D673D7}" name="Limitations" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{F9BDE932-EFFC-4548-B972-915DE6BB6C54}" name="Confidence" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{5533ACFD-5F82-4B79-BBA0-D9839EA8C868}" name="Evidence Type" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{628A541A-1065-4EFC-B499-CE6BEFE887E3}" name="URL" dataDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{FCFB7F89-AC1D-4887-8527-24B9868EAA03}" name="DOI" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4466,7 +4466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20563880-059C-45BC-AD28-51A92CA68829}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB4B6B3-FC56-412F-8BA2-C679AB1970AF}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4726,7 +4726,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3DB455-BA7B-47E3-BFFD-A6A006872EFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E7ED70B-96F7-4A4D-B91E-41E471B7642E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4917,7 +4917,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{386AB875-D5C6-4465-A300-9D4862B6ED79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4051A5-9180-4B26-8874-9666744FF777}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7903,63 +7903,63 @@
     <mergeCell ref="A2:R2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5:O56" xr:uid="{4226B330-8D54-436D-B168-D47293792162}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5:O56" xr:uid="{C595B6D9-3640-411A-B900-44E75B73BCBF}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="Q5" r:id="rId1" xr:uid="{50B98FD8-5DEA-4A61-8A75-85271DEAA6CE}"/>
-    <hyperlink ref="Q6" r:id="rId2" xr:uid="{600B3E94-DEE3-4A24-88BE-E96D0E50EC21}"/>
-    <hyperlink ref="Q7" r:id="rId3" xr:uid="{FEBFE3D7-8BA6-4A12-9BF3-1A9F8AC1C481}"/>
-    <hyperlink ref="Q8" r:id="rId4" xr:uid="{7522B2A9-C59D-4241-9FF2-92B7A06A3E83}"/>
-    <hyperlink ref="Q9" r:id="rId5" xr:uid="{7FC65319-0629-4915-8C58-FFBC903D268F}"/>
-    <hyperlink ref="Q10" r:id="rId6" xr:uid="{092D22D3-EF2A-4AC5-872F-70FD6DB5568B}"/>
-    <hyperlink ref="Q11" r:id="rId7" xr:uid="{5D80B620-7188-4588-A29D-0B7A925921F8}"/>
-    <hyperlink ref="Q12" r:id="rId8" xr:uid="{116C0B0C-7F77-4614-9A0B-F0F94D3C3550}"/>
-    <hyperlink ref="Q13" r:id="rId9" xr:uid="{C4D65907-C8A5-4549-A038-2BC608A7E829}"/>
-    <hyperlink ref="Q14" r:id="rId10" xr:uid="{0F436C2A-5BC9-4883-81D8-206E80339B23}"/>
-    <hyperlink ref="Q15" r:id="rId11" xr:uid="{A2D722DC-8C86-4139-A440-BCD6942E2088}"/>
-    <hyperlink ref="Q16" r:id="rId12" xr:uid="{D3676440-C9D5-4172-AF4E-21E24A3D951B}"/>
-    <hyperlink ref="Q17" r:id="rId13" xr:uid="{21422541-826F-435F-A434-558FA3D663F4}"/>
-    <hyperlink ref="Q18" r:id="rId14" xr:uid="{C7557186-0F2A-4F8D-8FC2-050A9E6A1ABF}"/>
-    <hyperlink ref="Q19" r:id="rId15" xr:uid="{80507FFD-39ED-4439-B13F-B59F465882EF}"/>
-    <hyperlink ref="Q20" r:id="rId16" xr:uid="{B0B8B6C7-55CD-48C0-9657-477E284080AF}"/>
-    <hyperlink ref="Q21" r:id="rId17" xr:uid="{26B4362B-541A-446B-B06B-56DE9F43703A}"/>
-    <hyperlink ref="Q22" r:id="rId18" xr:uid="{DB97CE44-2491-4193-B908-7B5CE4DDCD98}"/>
-    <hyperlink ref="Q23" r:id="rId19" xr:uid="{8AC3AEBD-DC77-4113-8539-D813614922C5}"/>
-    <hyperlink ref="Q24" r:id="rId20" xr:uid="{D8E25AB8-79A1-4DAA-9E31-B8EF53C3BBE3}"/>
-    <hyperlink ref="Q25" r:id="rId21" xr:uid="{0A4624E4-44F7-4103-8064-C8728703EC87}"/>
-    <hyperlink ref="Q26" r:id="rId22" xr:uid="{B29EFE77-452A-4538-A305-A25ED4E3B6FF}"/>
-    <hyperlink ref="Q27" r:id="rId23" xr:uid="{A70421E9-815B-45DA-9725-409B649C6A5F}"/>
-    <hyperlink ref="Q28" r:id="rId24" xr:uid="{E0F510F0-446E-4B8B-9165-9378457745DA}"/>
-    <hyperlink ref="Q29" r:id="rId25" xr:uid="{89D37078-F1EF-4EE8-99E6-18260A9739E0}"/>
-    <hyperlink ref="Q30" r:id="rId26" xr:uid="{8852B0FB-08F4-4DFA-B9EC-FD86B0C3792C}"/>
-    <hyperlink ref="Q31" r:id="rId27" xr:uid="{A56DE1BA-CCA5-45C2-A3D2-2D2AE29D89FD}"/>
-    <hyperlink ref="Q32" r:id="rId28" xr:uid="{F15EAC98-0934-4CE3-8370-D2257EC452E6}"/>
-    <hyperlink ref="Q33" r:id="rId29" xr:uid="{0E24D7CB-D5AF-442B-8858-198D2E7DAEA8}"/>
-    <hyperlink ref="Q34" r:id="rId30" xr:uid="{0E8B8D24-6149-4E66-A899-47889F319156}"/>
-    <hyperlink ref="Q35" r:id="rId31" xr:uid="{E67DDCE6-05F0-43C7-969F-D94D1E8F4E86}"/>
-    <hyperlink ref="Q36" r:id="rId32" xr:uid="{F17B9151-6D87-4166-9DBB-12AE911CCCAD}"/>
-    <hyperlink ref="Q37" r:id="rId33" xr:uid="{C1FFDF35-8553-4D01-BDA5-D8946F484648}"/>
-    <hyperlink ref="Q38" r:id="rId34" xr:uid="{A7D87DB3-63D9-4242-B499-E1815E771A80}"/>
-    <hyperlink ref="Q39" r:id="rId35" xr:uid="{61C78045-B540-404E-96A7-34EF4DE727B7}"/>
-    <hyperlink ref="Q40" r:id="rId36" xr:uid="{7C3FA33B-8F77-4594-A6FC-80F7E3F678EA}"/>
-    <hyperlink ref="Q41" r:id="rId37" xr:uid="{12BC12BD-46A6-4425-8842-2A24C220CE2F}"/>
-    <hyperlink ref="Q42" r:id="rId38" xr:uid="{48C3CE66-C7D2-4718-A015-C8D2B3316297}"/>
-    <hyperlink ref="Q43" r:id="rId39" xr:uid="{95717B5F-6F18-4DF7-9A07-FD8917D6D5EE}"/>
-    <hyperlink ref="Q44" r:id="rId40" xr:uid="{7D2C7950-0029-42ED-88F6-C6FA5F5D1F9D}"/>
-    <hyperlink ref="Q45" r:id="rId41" xr:uid="{12280006-19D5-4BD8-9AD0-47177C59BD2C}"/>
-    <hyperlink ref="Q46" r:id="rId42" xr:uid="{D4F6E8C5-C14B-4441-937D-D36ACABEBCFD}"/>
-    <hyperlink ref="Q47" r:id="rId43" display="https://www.worldbank.org/content/dam/Worldbank/document/SAR/nepal/PDNA Volume A Final.pdf" xr:uid="{E72EE081-0632-4A2F-8A38-C1378B0D07DF}"/>
-    <hyperlink ref="Q48" r:id="rId44" xr:uid="{01BB2104-0B11-4203-941A-00BC28A1231B}"/>
-    <hyperlink ref="Q49" r:id="rId45" xr:uid="{33291E89-6E81-4D96-BE5A-F4278DEB7B55}"/>
-    <hyperlink ref="Q50" r:id="rId46" xr:uid="{E948CDEC-6905-4022-A16C-CF26900F3910}"/>
-    <hyperlink ref="Q51" r:id="rId47" xr:uid="{E78F273C-E614-460D-B468-901DE202C23C}"/>
-    <hyperlink ref="Q52" r:id="rId48" xr:uid="{9582BB16-0265-4291-90D7-090D1B08BCAF}"/>
-    <hyperlink ref="Q53" r:id="rId49" xr:uid="{223BD69E-1002-4AA7-B303-DBF3877D8875}"/>
-    <hyperlink ref="Q54" r:id="rId50" xr:uid="{21C0FFA5-6CB1-4891-9536-ED4767213976}"/>
-    <hyperlink ref="Q55" r:id="rId51" xr:uid="{2AFE9900-167E-4DD5-90D2-6C73F808A8C5}"/>
-    <hyperlink ref="Q56" r:id="rId52" xr:uid="{CDDF38BD-2A65-40E6-8C43-FF1883F03F30}"/>
+    <hyperlink ref="Q5" r:id="rId1" xr:uid="{0C332003-2968-4C22-8F41-19C2207B9AC4}"/>
+    <hyperlink ref="Q6" r:id="rId2" xr:uid="{8D4476E2-A295-4BBD-B0AB-98B1FFA95F2B}"/>
+    <hyperlink ref="Q7" r:id="rId3" xr:uid="{01D00A43-2F12-4602-AEB6-7E375B0C1A7B}"/>
+    <hyperlink ref="Q8" r:id="rId4" xr:uid="{E908C4A4-F979-419A-9625-2FE9368A0174}"/>
+    <hyperlink ref="Q9" r:id="rId5" xr:uid="{076B71DB-D892-469F-B191-2BABC21A9ACB}"/>
+    <hyperlink ref="Q10" r:id="rId6" xr:uid="{AB3552C2-529A-444C-906A-CA8CC0E969D4}"/>
+    <hyperlink ref="Q11" r:id="rId7" xr:uid="{7CD17543-EA0B-4CA0-A1C0-AE3857DF6938}"/>
+    <hyperlink ref="Q12" r:id="rId8" xr:uid="{444D4FFA-D6C8-443D-A225-F7F6992F17EE}"/>
+    <hyperlink ref="Q13" r:id="rId9" xr:uid="{074E3478-28DA-4394-A344-7F685CD095F4}"/>
+    <hyperlink ref="Q14" r:id="rId10" xr:uid="{D7672833-D1FB-4A82-BD35-81BDB1618003}"/>
+    <hyperlink ref="Q15" r:id="rId11" xr:uid="{5745728F-431C-47E6-BF64-0D7BA09C0D80}"/>
+    <hyperlink ref="Q16" r:id="rId12" xr:uid="{87CCA08E-CBA3-44FF-95D5-93F04D909E38}"/>
+    <hyperlink ref="Q17" r:id="rId13" xr:uid="{5394B7CD-E6CC-4F8C-884A-07FCB7C654F8}"/>
+    <hyperlink ref="Q18" r:id="rId14" xr:uid="{CC4E9043-F6AF-452A-BC2B-A8425967A954}"/>
+    <hyperlink ref="Q19" r:id="rId15" xr:uid="{CEF434D1-E9B9-41EA-88EC-1285A7CC0163}"/>
+    <hyperlink ref="Q20" r:id="rId16" xr:uid="{84F335FA-6F7D-4B3B-A138-EAEF1DBC13A8}"/>
+    <hyperlink ref="Q21" r:id="rId17" xr:uid="{5848355B-A505-467A-B417-26DCE5AE0D3F}"/>
+    <hyperlink ref="Q22" r:id="rId18" xr:uid="{9013DBA9-DAA0-492E-B65D-CD1FC543CFB6}"/>
+    <hyperlink ref="Q23" r:id="rId19" xr:uid="{3C128AF1-E4A2-42BC-B888-B3EEF549BA0C}"/>
+    <hyperlink ref="Q24" r:id="rId20" xr:uid="{3B91E756-5B94-4EDE-BDC9-13DBE334028C}"/>
+    <hyperlink ref="Q25" r:id="rId21" xr:uid="{27DA6583-BCF1-415A-8360-5ED192A4A384}"/>
+    <hyperlink ref="Q26" r:id="rId22" xr:uid="{6E4E8EF7-DF26-4AA4-B7F6-5867A77268BF}"/>
+    <hyperlink ref="Q27" r:id="rId23" xr:uid="{542FF7F6-632A-470D-86BA-3A32A582D5B6}"/>
+    <hyperlink ref="Q28" r:id="rId24" xr:uid="{0FA2221D-4D9C-4199-95EF-4A963AA42E08}"/>
+    <hyperlink ref="Q29" r:id="rId25" xr:uid="{8EFCBD06-BD35-4103-A97B-92BF527FB1FC}"/>
+    <hyperlink ref="Q30" r:id="rId26" xr:uid="{9645BB30-453A-4B14-8FE1-90684762FF2D}"/>
+    <hyperlink ref="Q31" r:id="rId27" xr:uid="{0A0D7BDC-9F18-4B98-9BFA-1D9CD9BD005F}"/>
+    <hyperlink ref="Q32" r:id="rId28" xr:uid="{EDDBD2E1-BAA0-499B-A1CC-907840EBDDA1}"/>
+    <hyperlink ref="Q33" r:id="rId29" xr:uid="{78CF3FD7-59C6-4BD0-A231-186A1449A820}"/>
+    <hyperlink ref="Q34" r:id="rId30" xr:uid="{4C3767CB-BD2D-4EBF-9958-C8A4FE7ACAEE}"/>
+    <hyperlink ref="Q35" r:id="rId31" xr:uid="{274C27C6-9CDB-42A3-B56B-3CDAC98F9051}"/>
+    <hyperlink ref="Q36" r:id="rId32" xr:uid="{E1379A34-7327-4E0B-85EC-00F4296DC911}"/>
+    <hyperlink ref="Q37" r:id="rId33" xr:uid="{E9B22ABB-5D56-4FA7-A550-3C84B8C6E2EB}"/>
+    <hyperlink ref="Q38" r:id="rId34" xr:uid="{0A02D955-FC27-47CD-9D51-4095DAA93D58}"/>
+    <hyperlink ref="Q39" r:id="rId35" xr:uid="{D7B683CD-875E-4F64-8904-0A26182AABA4}"/>
+    <hyperlink ref="Q40" r:id="rId36" xr:uid="{DCC7A32B-6F0C-47D8-87C3-BB3E860D37E3}"/>
+    <hyperlink ref="Q41" r:id="rId37" xr:uid="{6D06116D-8C3D-476D-B745-17CDF7E75130}"/>
+    <hyperlink ref="Q42" r:id="rId38" xr:uid="{182E4810-C0F8-48B7-880A-6220EFAB3E22}"/>
+    <hyperlink ref="Q43" r:id="rId39" xr:uid="{8E093453-59AD-4728-859D-229C4CD54696}"/>
+    <hyperlink ref="Q44" r:id="rId40" xr:uid="{C2778417-C1D1-4736-8951-E9ADA2B6B841}"/>
+    <hyperlink ref="Q45" r:id="rId41" xr:uid="{99FE20E6-8298-4AEB-90E9-5CFC650DC44D}"/>
+    <hyperlink ref="Q46" r:id="rId42" xr:uid="{E9544DF7-499F-4E2C-80F6-CC9B8E210E9B}"/>
+    <hyperlink ref="Q47" r:id="rId43" display="https://www.worldbank.org/content/dam/Worldbank/document/SAR/nepal/PDNA Volume A Final.pdf" xr:uid="{E24E21A2-E37E-4705-9AE7-E43D3A16C029}"/>
+    <hyperlink ref="Q48" r:id="rId44" xr:uid="{35E2EBFE-6236-417D-9C19-5893A394C83D}"/>
+    <hyperlink ref="Q49" r:id="rId45" xr:uid="{620CCDD3-CD18-4163-9A48-1BE3A668A011}"/>
+    <hyperlink ref="Q50" r:id="rId46" xr:uid="{A3FF7F41-F920-4C6F-B8F0-67968D1AC2D0}"/>
+    <hyperlink ref="Q51" r:id="rId47" xr:uid="{F0D24951-2599-48BE-8DB1-2D2CA5FF801B}"/>
+    <hyperlink ref="Q52" r:id="rId48" xr:uid="{20E3D420-0BCF-4340-8893-1316AC361618}"/>
+    <hyperlink ref="Q53" r:id="rId49" xr:uid="{3DBC9159-FC9B-406B-BD50-2157CC7637D7}"/>
+    <hyperlink ref="Q54" r:id="rId50" xr:uid="{8DD64057-9DC7-4E0D-A6B1-A6680869E7B9}"/>
+    <hyperlink ref="Q55" r:id="rId51" xr:uid="{04A51330-1CAD-40E5-A798-9490778F8A14}"/>
+    <hyperlink ref="Q56" r:id="rId52" xr:uid="{F8E31554-420F-495B-B0F8-5BC49B31D3A8}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3888888888888889" bottom="0.3888888888888889" header="0.3" footer="0.19444444444444445"/>
@@ -7974,7 +7974,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D7CE0C-C560-46AE-BCE7-463298C97A22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39225756-889E-4B0C-B3E2-27B973B4EFE6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8450,21 +8450,21 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H5" r:id="rId1" xr:uid="{3215E1D8-0B34-449C-8279-C4D45C203CDE}"/>
-    <hyperlink ref="H6" r:id="rId2" xr:uid="{1B556A31-556F-45BB-8C49-D58DB9D5F1D4}"/>
-    <hyperlink ref="H7" r:id="rId3" xr:uid="{F6248226-D148-4FFB-A3BA-ED21FC7B1692}"/>
-    <hyperlink ref="H8" r:id="rId4" xr:uid="{F1527C28-831A-491E-B83F-BE95B4DBA37C}"/>
-    <hyperlink ref="H9" r:id="rId5" xr:uid="{E88997E4-2F47-4114-9805-7D9EA54626FD}"/>
-    <hyperlink ref="H10" r:id="rId6" xr:uid="{0EA008EA-39B1-4165-89B8-855FF61DEE03}"/>
-    <hyperlink ref="H11" r:id="rId7" xr:uid="{4BD600E2-9B9F-47AF-BF3C-ADDF8164140D}"/>
-    <hyperlink ref="H12" r:id="rId8" xr:uid="{EE1286E2-C56A-4A18-8AF1-ABF4573B9A26}"/>
-    <hyperlink ref="H13" r:id="rId9" xr:uid="{F815FA9E-A00B-4306-91E7-A2465E3B25AE}"/>
-    <hyperlink ref="H14" r:id="rId10" xr:uid="{5FF0A2C5-2DD2-41AD-BC0A-63F80D2F5CC7}"/>
-    <hyperlink ref="H15" r:id="rId11" xr:uid="{5712E5FE-B143-4668-B4FC-27C628E221C7}"/>
-    <hyperlink ref="H16" r:id="rId12" xr:uid="{C8DBCAF8-5375-4DB6-A10F-CD706286F1EF}"/>
-    <hyperlink ref="H17" r:id="rId13" xr:uid="{1EC7E7A6-5042-466E-AF2F-86FA507A9AC0}"/>
-    <hyperlink ref="H18" r:id="rId14" xr:uid="{7146DFC8-DB93-4C04-8A57-C0DDEDE760B5}"/>
-    <hyperlink ref="H19" r:id="rId15" xr:uid="{14142D2C-E021-4B45-AABA-4F520FA50052}"/>
+    <hyperlink ref="H5" r:id="rId1" xr:uid="{058858FE-AE0F-4B71-BDE7-D026A33CA2E6}"/>
+    <hyperlink ref="H6" r:id="rId2" xr:uid="{F2B7FF52-ECFB-4EF6-A1FA-F987CDDCE450}"/>
+    <hyperlink ref="H7" r:id="rId3" xr:uid="{D7524D51-F811-4DEF-80E9-C84C7859458F}"/>
+    <hyperlink ref="H8" r:id="rId4" xr:uid="{C17E6CCF-A130-48A6-9BA9-42010644A879}"/>
+    <hyperlink ref="H9" r:id="rId5" xr:uid="{90F8FDB9-AA69-4787-AD50-EF529650A996}"/>
+    <hyperlink ref="H10" r:id="rId6" xr:uid="{8E61A8DF-478B-442A-8116-2579174BF9FE}"/>
+    <hyperlink ref="H11" r:id="rId7" xr:uid="{569CB69D-9226-4EE2-9456-6B19CF230C7F}"/>
+    <hyperlink ref="H12" r:id="rId8" xr:uid="{3B3734C4-5817-49D3-9989-478CA2C8575F}"/>
+    <hyperlink ref="H13" r:id="rId9" xr:uid="{C526A031-FF30-4601-AA6C-A49DCBB095BE}"/>
+    <hyperlink ref="H14" r:id="rId10" xr:uid="{11DC8EDD-9246-46F2-BB8A-587B9BE30C37}"/>
+    <hyperlink ref="H15" r:id="rId11" xr:uid="{A4C4922E-D905-467F-83C7-60A854416B4A}"/>
+    <hyperlink ref="H16" r:id="rId12" xr:uid="{97A04386-29FD-4B76-9245-405294B58A2B}"/>
+    <hyperlink ref="H17" r:id="rId13" xr:uid="{2D91FB03-69D3-458D-B330-56931EBB4216}"/>
+    <hyperlink ref="H18" r:id="rId14" xr:uid="{00B0EBD9-194B-4AFD-AAB3-D35B2FFFCEAD}"/>
+    <hyperlink ref="H19" r:id="rId15" xr:uid="{A2503E8C-88EE-4633-97C3-68FF6A8080B5}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3888888888888889" bottom="0.3888888888888889" header="0.3" footer="0.19444444444444445"/>
@@ -8476,7 +8476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F24F4D72-1E70-4655-AE77-9C44902CAE3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9617BB79-3429-444F-B289-FCF5C5CFC380}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8607,7 +8607,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45AA6DCD-8ED3-467A-8F80-A317984CC077}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193E4497-C0D4-495C-8041-7829F47D3394}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -9015,7 +9015,7 @@
         <v>145</v>
       </c>
       <c r="B36" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -9023,7 +9023,7 @@
         <v>157</v>
       </c>
       <c r="B37" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -9057,7 +9057,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF581F2A-344C-4B05-AA94-A0F3D5DFE3D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09EDB23-9F10-457D-87EF-1D4A2C720395}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -9207,7 +9207,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E536C9C-2C45-4B82-8E16-B7E39E995E7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3B3F86-769E-4DB6-806B-78303D0CCD02}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/reporting-site/public/reviews/task31/artifacts/Asia_Pacific_Welfare_Losses_Evidence_Register_2026.xlsx
+++ b/reporting-site/public/reviews/task31/artifacts/Asia_Pacific_Welfare_Losses_Evidence_Register_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Raymond\OneDrive\Desktop\ADB\Research\Task31\outputs\task31_welfare_review_20260804\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{655C3B44-6E86-4335-BDDA-0D86EC3B92F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A77F126B-6ADF-4C24-969D-CFE69000CF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1380" windowWidth="4365" windowHeight="2820" xr2:uid="{A9AF3348-2B31-417F-88DA-41AE955719BD}"/>
+    <workbookView xWindow="1380" yWindow="1380" windowWidth="4365" windowHeight="2820" xr2:uid="{71789420-CE43-49EA-80AF-055733162645}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,11 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Confidence Rubric'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Dashboard!$A$1:$K$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Evidence!$A$1:$R$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Evidence!$A$1:$R$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Figure Data'!$A$1:$D$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Key Estimates'!$A$1:$H$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">README!$A$1:$F$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">References!$A$1:$C$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">References!$A$1:$C$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Search Log'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="972">
   <si>
     <t>Welfare losses evidence register</t>
   </si>
@@ -2281,6 +2281,129 @@
     <t>10.1038/s41893-020-00610-5</t>
   </si>
   <si>
+    <t>N25</t>
+  </si>
+  <si>
+    <t>Banerjee and Maharaj (2019)</t>
+  </si>
+  <si>
+    <t>Journal of Development Economics</t>
+  </si>
+  <si>
+    <t>Rural India</t>
+  </si>
+  <si>
+    <t>Infants exposed in utero</t>
+  </si>
+  <si>
+    <t>Extreme heat during pregnancy</t>
+  </si>
+  <si>
+    <t>Infant mortality</t>
+  </si>
+  <si>
+    <t>About 2 additional children die as infants per 1,000 births following high temperature during pregnancy; the relationship holds in rural India only</t>
+  </si>
+  <si>
+    <t>Temperature exposure during gestation linked to infant survival, with phased programme rollout used for identification</t>
+  </si>
+  <si>
+    <t>Quasi-experimental; employment-guarantee and community-health-worker rollouts exploited as adaptation margins</t>
+  </si>
+  <si>
+    <t>Mechanism is inferred rather than directly measured (reduced yields, wages, and diarrhoeal disease); the estimate is rural and may not transfer to urban exposure. Only the health-worker programme modified the temperature-mortality relationship; the employment guarantee did not</t>
+  </si>
+  <si>
+    <t>Quasi-experimental cohort</t>
+  </si>
+  <si>
+    <t>https://uoe.figshare.com/articles/Heat_infant_mortality_and_adaptation_Evidence_from_India/29762129</t>
+  </si>
+  <si>
+    <t>10.1016/j.jdeveco.2019.102378</t>
+  </si>
+  <si>
+    <t>N26</t>
+  </si>
+  <si>
+    <t>Tiwari, Jacoby, and Skoufias (2016)</t>
+  </si>
+  <si>
+    <t>Economic Development and Cultural Change</t>
+  </si>
+  <si>
+    <t>Rural Nepal</t>
+  </si>
+  <si>
+    <t>Children aged 0-60 months</t>
+  </si>
+  <si>
+    <t>Monsoon rainfall shocks</t>
+  </si>
+  <si>
+    <t>Child weight-for-height and height</t>
+  </si>
+  <si>
+    <t>A 10% increase in monsoon rainfall above historic norms raises weight-for-height by 0.13 standard deviations, combining a negative disease-environment effect of at most 0.04 SD with an income effect as high as 0.17 SD; the height gain is transitory and dissipates by age 5</t>
+  </si>
+  <si>
+    <t>Rainfall-shock timing interacted with agricultural seasonality to isolate income from disease channels</t>
+  </si>
+  <si>
+    <t>Quasi-experimental use of monsoon timing</t>
+  </si>
+  <si>
+    <t>Identifies the income channel for a rainfall surplus rather than a drought deficit; the height effect is explicitly transitory, so this record does not support a long-run human-capital claim</t>
+  </si>
+  <si>
+    <t>Quasi-experimental anthropometric study</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1086/689308</t>
+  </si>
+  <si>
+    <t>10.1086/689308</t>
+  </si>
+  <si>
+    <t>N27</t>
+  </si>
+  <si>
+    <t>Giannelli and Canessa (2021)</t>
+  </si>
+  <si>
+    <t>Rural Bangladesh</t>
+  </si>
+  <si>
+    <t>Rural households across the wealth distribution</t>
+  </si>
+  <si>
+    <t>August-September 2014 flood</t>
+  </si>
+  <si>
+    <t>Income, expenditure, nutrition, and migration</t>
+  </si>
+  <si>
+    <t>Most-affected households saw significant drops in income and expenditure; internal migration rose 7 percentage points among low-wealth households and international migration 3 points among high-wealth households; remittances to poorer households offset roughly 40% of the decline in farm self-employment income and half the decline in food expenditure</t>
+  </si>
+  <si>
+    <t>Georeferenced flood mapping matched to a household panel; difference-in-differences with fixed effects</t>
+  </si>
+  <si>
+    <t>Difference-in-differences on geographic flood exposure</t>
+  </si>
+  <si>
+    <t>Coping capacity is stratified by pre-shock wealth, so the averages conceal that the poorest substitute internal migration for the international migration only wealthier households can afford</t>
+  </si>
+  <si>
+    <t>Quasi-experimental household panel</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1086/713939</t>
+  </si>
+  <si>
+    <t>10.1086/713939</t>
+  </si>
+  <si>
     <t>Key quantitative estimates</t>
   </si>
   <si>
@@ -2767,7 +2890,13 @@
     <t>World Health Organization. (2022). Global Excess Deaths Associated with the COVID-19 Pandemic, 2020-2021. Geneva: WHO.</t>
   </si>
   <si>
-    <t>Yarrow, N., Masood, E., and Afkar, R. (2020). Estimates of COVID-19 Impacts on Learning and Earning in Indonesia: How to Turn the Tide. Washington, DC: World Bank.</t>
+    <t>Yarrow, N., Masood, E., and Afkar, R. (2020). Estimates of COVID-19 Impacts on Learning and Earning in Indonesia: How to Turn the Tide. Washington, DC: World Bank.Banerjee, R., and Maharaj, R. (2019). Heat, infant mortality, and adaptation: Evidence from India. Journal of Development Economics. https://doi.org/10.1016/j.jdeveco.2019.102378</t>
+  </si>
+  <si>
+    <t>Giannelli, G. C., and Canessa, E. (2021). After the Flood: Migration and Remittances as Coping Strategies of Rural Bangladeshi Households. Economic Development and Cultural Change. https://doi.org/10.1086/713939</t>
+  </si>
+  <si>
+    <t>Tiwari, S., Jacoby, H. G., and Skoufias, E. (2016). Monsoon Babies: Rainfall Shocks and Child Nutrition in Nepal. Economic Development and Cultural Change. https://doi.org/10.1086/689308</t>
   </si>
   <si>
     <t>Asia-Pacific welfare-loss evidence dashboard</t>
@@ -3981,14 +4110,14 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1C3C-4FF8-8145-7AF6CB0E78E5}"/>
+              <c16:uniqueId val="{00000002-CA05-423B-9B88-40E07BC0BCDC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4001,11 +4130,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="874096383"/>
-        <c:axId val="874103583"/>
+        <c:axId val="937892144"/>
+        <c:axId val="937893104"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="874096383"/>
+        <c:axId val="937892144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4015,7 +4144,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="874103583"/>
+        <c:crossAx val="937893104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4023,7 +4152,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="874103583"/>
+        <c:axId val="937893104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4034,7 +4163,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="874096383"/>
+        <c:crossAx val="937892144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4102,7 +4231,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC2D0E86-6C1E-4168-2739-89218884055C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2CFC370-9F6C-9EA3-0AC6-EF9AE6B30D8E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4124,27 +4253,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B8619403-CE21-46A7-AF88-CE7029EC5606}" name="EvidenceTable" displayName="EvidenceTable" ref="A4:R56" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
-  <autoFilter ref="A4:R56" xr:uid="{B8619403-CE21-46A7-AF88-CE7029EC5606}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E926FF29-EACA-4636-8A32-D714EC331C99}" name="EvidenceTable" displayName="EvidenceTable" ref="A4:R59" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+  <autoFilter ref="A4:R59" xr:uid="{E926FF29-EACA-4636-8A32-D714EC331C99}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{B3FA3C08-C0F6-422A-908C-0C744612F45F}" name="ID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{AE0F1CC6-9119-40C1-807C-131133867D0A}" name="Category" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{A42FD296-1C89-42BA-8260-6886085B582B}" name="Study" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{84B47023-E2BA-44CE-B2BC-CBD694436B51}" name="Year" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{20921EFD-BC60-4888-B7C3-F2E68F797453}" name="Source" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{3B181883-EAE5-4C3E-99BF-9A60EC1814F0}" name="Geography" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{7FF065D4-0529-4BFC-8A6C-4BC630288B92}" name="Subregion" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{A79869C3-B49A-467F-8C35-B3EEC2BC8863}" name="Population" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{9996BE64-8891-4BBE-8472-8087358ACA93}" name="Shock" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{CEB475BB-92A1-40AF-B987-AA7D1F0832C7}" name="Welfare Indicator" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{2A0BB8F8-A434-467E-9812-5DD934E7C7E3}" name="Estimate" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{8CAA49FE-5966-4BC8-9353-4D0BECFAF297}" name="Methodology" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{415D5427-5FB6-4A7E-A058-23A7F09F292E}" name="Identification" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{7AF0A998-C35B-4423-AC46-1E7329D673D7}" name="Limitations" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{F9BDE932-EFFC-4548-B972-915DE6BB6C54}" name="Confidence" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{5533ACFD-5F82-4B79-BBA0-D9839EA8C868}" name="Evidence Type" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{628A541A-1065-4EFC-B499-CE6BEFE887E3}" name="URL" dataDxfId="0"/>
-    <tableColumn id="18" xr3:uid="{FCFB7F89-AC1D-4887-8527-24B9868EAA03}" name="DOI" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{A699042E-9D55-4AF1-93C4-CFD67498F039}" name="ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{A3CE8752-D3C4-4B63-9E52-86D68C417CF8}" name="Category" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{6A49B28E-7D87-42B8-ADD2-940331B8D64B}" name="Study" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{9B57F65E-FF1F-41EC-BAC6-789FFF264C0C}" name="Year" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{E4579502-C6BD-4579-AD93-E6C79059A575}" name="Source" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{D9ED3A83-6150-4BA2-87BD-E3DD7D5F756F}" name="Geography" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{3BD187C6-D8FC-40CA-B5C8-A02E4C297FA2}" name="Subregion" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{2F4507CD-015F-4DDD-B80C-80490A575C52}" name="Population" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{72EFC807-A691-4279-ABAF-C70E1C6C4D93}" name="Shock" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{969425AB-FFE5-4745-89F8-A719AE03B156}" name="Welfare Indicator" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{89FD63C1-3465-4FA6-BC72-360C2D3A5208}" name="Estimate" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{E723DB08-915D-4647-98D7-E2B5E8EC3A0B}" name="Methodology" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{54457B76-FBFB-44BE-90B9-A3D7E887C66A}" name="Identification" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{C848C2E3-3E3F-4196-9C94-60DC27CF46C2}" name="Limitations" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{5237D108-D0B1-46BB-B2C8-50C6C49F648A}" name="Confidence" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{ADD5CFFA-D18C-415E-955B-2A6D61AF0AF5}" name="Evidence Type" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{6D088BA7-2F4E-46C4-9B96-E4E3350FC88A}" name="URL" dataDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{7E6AAADA-EF8C-4F1B-9398-B6155AC0D935}" name="DOI" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4466,7 +4595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB4B6B3-FC56-412F-8BA2-C679AB1970AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5883C86C-13C3-435E-A556-E4D508D3F2C0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4485,7 +4614,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>904</v>
+        <v>947</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4500,7 +4629,7 @@
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>905</v>
+        <v>948</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4515,7 +4644,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="30" t="s">
-        <v>906</v>
+        <v>949</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -4530,87 +4659,87 @@
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
-        <v>907</v>
+        <v>950</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>771</v>
+        <v>812</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>908</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
-        <v>909</v>
+        <v>952</v>
       </c>
       <c r="B7" s="31">
         <f>ROWS(EvidenceTable[ID])</f>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>910</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
-        <v>911</v>
+        <v>954</v>
       </c>
       <c r="B8" s="31">
         <f>COUNTIF(EvidenceTable[Source],"*Journal*")+COUNTIF(EvidenceTable[Source],"Nature*")+COUNTIF(EvidenceTable[Source],"Science*")+COUNTIF(EvidenceTable[Source],"The Lancet*")+COUNTIF(EvidenceTable[Source],"Proceedings*")+COUNTIF(EvidenceTable[Source],"World Development")+COUNTIF(EvidenceTable[Source],"Quarterly*")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>912</v>
+        <v>955</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
-        <v>913</v>
+        <v>956</v>
       </c>
       <c r="B9" s="31">
         <f>COUNTIF(EvidenceTable[Confidence],"High")</f>
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>914</v>
+        <v>957</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="27" t="s">
-        <v>915</v>
+        <v>958</v>
       </c>
       <c r="B10" s="31">
         <f>COUNTIF(EvidenceTable[Confidence],"Medium")</f>
         <v>34</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>916</v>
+        <v>959</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="27" t="s">
-        <v>917</v>
+        <v>960</v>
       </c>
       <c r="B11" s="31">
         <f>COUNTIF(EvidenceTable[Confidence],"Low")</f>
         <v>1</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>918</v>
+        <v>961</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="26" t="s">
-        <v>919</v>
+        <v>962</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>909</v>
+        <v>952</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>909</v>
+        <v>952</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -4626,7 +4755,7 @@
       </c>
       <c r="F14" s="32">
         <f>COUNTIF(EvidenceTable[Confidence],E14)</f>
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -4651,7 +4780,7 @@
       </c>
       <c r="B16" s="33">
         <f>COUNTIF(EvidenceTable[Category],A16)</f>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E16" s="32" t="s">
         <v>384</v>
@@ -4663,7 +4792,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="34" t="s">
-        <v>920</v>
+        <v>963</v>
       </c>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -4678,34 +4807,34 @@
     </row>
     <row r="20" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="35" t="s">
-        <v>921</v>
+        <v>964</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>922</v>
+        <v>965</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="35" t="s">
-        <v>923</v>
+        <v>966</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>924</v>
+        <v>967</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
-        <v>925</v>
+        <v>968</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>926</v>
+        <v>969</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="35" t="s">
-        <v>927</v>
+        <v>970</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>928</v>
+        <v>971</v>
       </c>
     </row>
   </sheetData>
@@ -4726,7 +4855,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E7ED70B-96F7-4A4D-B91E-41E471B7642E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF7550D6-A9D0-485A-BA5D-69CFBEA62F92}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4917,11 +5046,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4051A5-9180-4B26-8874-9666744FF777}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B95C6F-0A6E-4880-B572-E0B0962604DD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -7842,59 +7971,227 @@
       </c>
     </row>
     <row r="56" spans="1:18" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="11" t="s">
         <v>726</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="D56" s="20">
+      <c r="D56" s="19">
         <v>2021</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="10" t="s">
         <v>728</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="10" t="s">
         <v>729</v>
       </c>
-      <c r="G56" s="17" t="s">
+      <c r="G56" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="H56" s="17" t="s">
+      <c r="H56" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="I56" s="17" t="s">
+      <c r="I56" s="10" t="s">
         <v>732</v>
       </c>
-      <c r="J56" s="17" t="s">
+      <c r="J56" s="10" t="s">
         <v>733</v>
       </c>
-      <c r="K56" s="17" t="s">
+      <c r="K56" s="10" t="s">
         <v>734</v>
       </c>
-      <c r="L56" s="17" t="s">
+      <c r="L56" s="10" t="s">
         <v>735</v>
       </c>
-      <c r="M56" s="17" t="s">
+      <c r="M56" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="N56" s="17" t="s">
+      <c r="N56" s="10" t="s">
         <v>737</v>
       </c>
-      <c r="O56" s="17" t="s">
+      <c r="O56" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="P56" s="17" t="s">
+      <c r="P56" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="Q56" s="22" t="s">
+      <c r="Q56" s="21" t="s">
         <v>739</v>
       </c>
-      <c r="R56" s="18" t="s">
+      <c r="R56" s="12" t="s">
         <v>740</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="11" t="s">
+        <v>741</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="D57" s="19">
+        <v>2019</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="J57" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>750</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="O57" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q57" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="R57" s="12" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="11" t="s">
+        <v>755</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>756</v>
+      </c>
+      <c r="D58" s="19">
+        <v>2016</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>757</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>758</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>759</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>760</v>
+      </c>
+      <c r="J58" s="10" t="s">
+        <v>761</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>762</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>763</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>764</v>
+      </c>
+      <c r="N58" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="O58" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="Q58" s="21" t="s">
+        <v>767</v>
+      </c>
+      <c r="R58" s="12" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>770</v>
+      </c>
+      <c r="D59" s="20">
+        <v>2021</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>771</v>
+      </c>
+      <c r="G59" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>772</v>
+      </c>
+      <c r="I59" s="17" t="s">
+        <v>773</v>
+      </c>
+      <c r="J59" s="17" t="s">
+        <v>774</v>
+      </c>
+      <c r="K59" s="17" t="s">
+        <v>775</v>
+      </c>
+      <c r="L59" s="17" t="s">
+        <v>776</v>
+      </c>
+      <c r="M59" s="17" t="s">
+        <v>777</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>778</v>
+      </c>
+      <c r="O59" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="P59" s="17" t="s">
+        <v>779</v>
+      </c>
+      <c r="Q59" s="22" t="s">
+        <v>780</v>
+      </c>
+      <c r="R59" s="18" t="s">
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -7903,78 +8200,81 @@
     <mergeCell ref="A2:R2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5:O56" xr:uid="{C595B6D9-3640-411A-B900-44E75B73BCBF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5:O59" xr:uid="{7B1CBE2F-C370-41C1-812B-91D9D2E9D815}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="Q5" r:id="rId1" xr:uid="{0C332003-2968-4C22-8F41-19C2207B9AC4}"/>
-    <hyperlink ref="Q6" r:id="rId2" xr:uid="{8D4476E2-A295-4BBD-B0AB-98B1FFA95F2B}"/>
-    <hyperlink ref="Q7" r:id="rId3" xr:uid="{01D00A43-2F12-4602-AEB6-7E375B0C1A7B}"/>
-    <hyperlink ref="Q8" r:id="rId4" xr:uid="{E908C4A4-F979-419A-9625-2FE9368A0174}"/>
-    <hyperlink ref="Q9" r:id="rId5" xr:uid="{076B71DB-D892-469F-B191-2BABC21A9ACB}"/>
-    <hyperlink ref="Q10" r:id="rId6" xr:uid="{AB3552C2-529A-444C-906A-CA8CC0E969D4}"/>
-    <hyperlink ref="Q11" r:id="rId7" xr:uid="{7CD17543-EA0B-4CA0-A1C0-AE3857DF6938}"/>
-    <hyperlink ref="Q12" r:id="rId8" xr:uid="{444D4FFA-D6C8-443D-A225-F7F6992F17EE}"/>
-    <hyperlink ref="Q13" r:id="rId9" xr:uid="{074E3478-28DA-4394-A344-7F685CD095F4}"/>
-    <hyperlink ref="Q14" r:id="rId10" xr:uid="{D7672833-D1FB-4A82-BD35-81BDB1618003}"/>
-    <hyperlink ref="Q15" r:id="rId11" xr:uid="{5745728F-431C-47E6-BF64-0D7BA09C0D80}"/>
-    <hyperlink ref="Q16" r:id="rId12" xr:uid="{87CCA08E-CBA3-44FF-95D5-93F04D909E38}"/>
-    <hyperlink ref="Q17" r:id="rId13" xr:uid="{5394B7CD-E6CC-4F8C-884A-07FCB7C654F8}"/>
-    <hyperlink ref="Q18" r:id="rId14" xr:uid="{CC4E9043-F6AF-452A-BC2B-A8425967A954}"/>
-    <hyperlink ref="Q19" r:id="rId15" xr:uid="{CEF434D1-E9B9-41EA-88EC-1285A7CC0163}"/>
-    <hyperlink ref="Q20" r:id="rId16" xr:uid="{84F335FA-6F7D-4B3B-A138-EAEF1DBC13A8}"/>
-    <hyperlink ref="Q21" r:id="rId17" xr:uid="{5848355B-A505-467A-B417-26DCE5AE0D3F}"/>
-    <hyperlink ref="Q22" r:id="rId18" xr:uid="{9013DBA9-DAA0-492E-B65D-CD1FC543CFB6}"/>
-    <hyperlink ref="Q23" r:id="rId19" xr:uid="{3C128AF1-E4A2-42BC-B888-B3EEF549BA0C}"/>
-    <hyperlink ref="Q24" r:id="rId20" xr:uid="{3B91E756-5B94-4EDE-BDC9-13DBE334028C}"/>
-    <hyperlink ref="Q25" r:id="rId21" xr:uid="{27DA6583-BCF1-415A-8360-5ED192A4A384}"/>
-    <hyperlink ref="Q26" r:id="rId22" xr:uid="{6E4E8EF7-DF26-4AA4-B7F6-5867A77268BF}"/>
-    <hyperlink ref="Q27" r:id="rId23" xr:uid="{542FF7F6-632A-470D-86BA-3A32A582D5B6}"/>
-    <hyperlink ref="Q28" r:id="rId24" xr:uid="{0FA2221D-4D9C-4199-95EF-4A963AA42E08}"/>
-    <hyperlink ref="Q29" r:id="rId25" xr:uid="{8EFCBD06-BD35-4103-A97B-92BF527FB1FC}"/>
-    <hyperlink ref="Q30" r:id="rId26" xr:uid="{9645BB30-453A-4B14-8FE1-90684762FF2D}"/>
-    <hyperlink ref="Q31" r:id="rId27" xr:uid="{0A0D7BDC-9F18-4B98-9BFA-1D9CD9BD005F}"/>
-    <hyperlink ref="Q32" r:id="rId28" xr:uid="{EDDBD2E1-BAA0-499B-A1CC-907840EBDDA1}"/>
-    <hyperlink ref="Q33" r:id="rId29" xr:uid="{78CF3FD7-59C6-4BD0-A231-186A1449A820}"/>
-    <hyperlink ref="Q34" r:id="rId30" xr:uid="{4C3767CB-BD2D-4EBF-9958-C8A4FE7ACAEE}"/>
-    <hyperlink ref="Q35" r:id="rId31" xr:uid="{274C27C6-9CDB-42A3-B56B-3CDAC98F9051}"/>
-    <hyperlink ref="Q36" r:id="rId32" xr:uid="{E1379A34-7327-4E0B-85EC-00F4296DC911}"/>
-    <hyperlink ref="Q37" r:id="rId33" xr:uid="{E9B22ABB-5D56-4FA7-A550-3C84B8C6E2EB}"/>
-    <hyperlink ref="Q38" r:id="rId34" xr:uid="{0A02D955-FC27-47CD-9D51-4095DAA93D58}"/>
-    <hyperlink ref="Q39" r:id="rId35" xr:uid="{D7B683CD-875E-4F64-8904-0A26182AABA4}"/>
-    <hyperlink ref="Q40" r:id="rId36" xr:uid="{DCC7A32B-6F0C-47D8-87C3-BB3E860D37E3}"/>
-    <hyperlink ref="Q41" r:id="rId37" xr:uid="{6D06116D-8C3D-476D-B745-17CDF7E75130}"/>
-    <hyperlink ref="Q42" r:id="rId38" xr:uid="{182E4810-C0F8-48B7-880A-6220EFAB3E22}"/>
-    <hyperlink ref="Q43" r:id="rId39" xr:uid="{8E093453-59AD-4728-859D-229C4CD54696}"/>
-    <hyperlink ref="Q44" r:id="rId40" xr:uid="{C2778417-C1D1-4736-8951-E9ADA2B6B841}"/>
-    <hyperlink ref="Q45" r:id="rId41" xr:uid="{99FE20E6-8298-4AEB-90E9-5CFC650DC44D}"/>
-    <hyperlink ref="Q46" r:id="rId42" xr:uid="{E9544DF7-499F-4E2C-80F6-CC9B8E210E9B}"/>
-    <hyperlink ref="Q47" r:id="rId43" display="https://www.worldbank.org/content/dam/Worldbank/document/SAR/nepal/PDNA Volume A Final.pdf" xr:uid="{E24E21A2-E37E-4705-9AE7-E43D3A16C029}"/>
-    <hyperlink ref="Q48" r:id="rId44" xr:uid="{35E2EBFE-6236-417D-9C19-5893A394C83D}"/>
-    <hyperlink ref="Q49" r:id="rId45" xr:uid="{620CCDD3-CD18-4163-9A48-1BE3A668A011}"/>
-    <hyperlink ref="Q50" r:id="rId46" xr:uid="{A3FF7F41-F920-4C6F-B8F0-67968D1AC2D0}"/>
-    <hyperlink ref="Q51" r:id="rId47" xr:uid="{F0D24951-2599-48BE-8DB1-2D2CA5FF801B}"/>
-    <hyperlink ref="Q52" r:id="rId48" xr:uid="{20E3D420-0BCF-4340-8893-1316AC361618}"/>
-    <hyperlink ref="Q53" r:id="rId49" xr:uid="{3DBC9159-FC9B-406B-BD50-2157CC7637D7}"/>
-    <hyperlink ref="Q54" r:id="rId50" xr:uid="{8DD64057-9DC7-4E0D-A6B1-A6680869E7B9}"/>
-    <hyperlink ref="Q55" r:id="rId51" xr:uid="{04A51330-1CAD-40E5-A798-9490778F8A14}"/>
-    <hyperlink ref="Q56" r:id="rId52" xr:uid="{F8E31554-420F-495B-B0F8-5BC49B31D3A8}"/>
+    <hyperlink ref="Q5" r:id="rId1" xr:uid="{DF1031D9-0E5D-4543-9C35-54452D37ACD8}"/>
+    <hyperlink ref="Q6" r:id="rId2" xr:uid="{2811470A-28F0-4D9E-849D-5775F77F66A8}"/>
+    <hyperlink ref="Q7" r:id="rId3" xr:uid="{E739AE59-D03D-470B-91A6-6461D9FD142C}"/>
+    <hyperlink ref="Q8" r:id="rId4" xr:uid="{49CDD9AD-C0F4-450E-9B6E-8A5898FF7188}"/>
+    <hyperlink ref="Q9" r:id="rId5" xr:uid="{771B75F8-39E3-4B86-AE84-D52D56C53B8A}"/>
+    <hyperlink ref="Q10" r:id="rId6" xr:uid="{4C6864CB-0562-4C54-AA29-6DE85FBB1E63}"/>
+    <hyperlink ref="Q11" r:id="rId7" xr:uid="{ECFFAE5A-4184-4DBD-B753-F469FFE000CD}"/>
+    <hyperlink ref="Q12" r:id="rId8" xr:uid="{0BE39899-448C-46CD-A7AA-5018066D7F33}"/>
+    <hyperlink ref="Q13" r:id="rId9" xr:uid="{FCC18E01-6686-465B-82A1-AC4DE1F37931}"/>
+    <hyperlink ref="Q14" r:id="rId10" xr:uid="{3B01E7BC-D1BD-4DD7-B1E2-932738345E3C}"/>
+    <hyperlink ref="Q15" r:id="rId11" xr:uid="{D812DF4E-AE49-4F70-8418-F992D8888A9D}"/>
+    <hyperlink ref="Q16" r:id="rId12" xr:uid="{264F4447-3340-4052-83AA-3DB26CE8C7AD}"/>
+    <hyperlink ref="Q17" r:id="rId13" xr:uid="{170ADB16-52B8-4188-9649-CF35C9FE6054}"/>
+    <hyperlink ref="Q18" r:id="rId14" xr:uid="{DE3D0780-70AC-461C-A3C1-F5B11E42D3B7}"/>
+    <hyperlink ref="Q19" r:id="rId15" xr:uid="{4068BA23-4B41-440F-9645-91A7677F34EF}"/>
+    <hyperlink ref="Q20" r:id="rId16" xr:uid="{F51DC8B1-CE3C-42F6-B7AE-C832242897D3}"/>
+    <hyperlink ref="Q21" r:id="rId17" xr:uid="{FFD66CDE-E08F-466B-96B7-DA44D5FBD792}"/>
+    <hyperlink ref="Q22" r:id="rId18" xr:uid="{AD1EBEB8-DE23-420C-B724-99F1293E0206}"/>
+    <hyperlink ref="Q23" r:id="rId19" xr:uid="{43EFB4FC-7632-4272-A18F-FB614351A30F}"/>
+    <hyperlink ref="Q24" r:id="rId20" xr:uid="{01F6C2F6-7EE5-4A55-A38F-6162C02E3B83}"/>
+    <hyperlink ref="Q25" r:id="rId21" xr:uid="{7343D18A-EE7D-4CBC-93BD-F085EAA3AA60}"/>
+    <hyperlink ref="Q26" r:id="rId22" xr:uid="{C6C10368-89E2-4D29-9546-4225155EF8EF}"/>
+    <hyperlink ref="Q27" r:id="rId23" xr:uid="{B8BB4A4F-8068-4D74-8E41-CC356D357BBC}"/>
+    <hyperlink ref="Q28" r:id="rId24" xr:uid="{0C8109AD-50ED-4CED-88C6-73C023E442D3}"/>
+    <hyperlink ref="Q29" r:id="rId25" xr:uid="{C4A06113-FFBA-4EB7-B540-34F264D79676}"/>
+    <hyperlink ref="Q30" r:id="rId26" xr:uid="{5CC8C8C3-4895-4061-AFC7-5C078B460889}"/>
+    <hyperlink ref="Q31" r:id="rId27" xr:uid="{FCCB952C-D9EF-49ED-9647-DD3BAD1656C3}"/>
+    <hyperlink ref="Q32" r:id="rId28" xr:uid="{9032671A-FE70-433B-B3C6-D7FCAA1F7803}"/>
+    <hyperlink ref="Q33" r:id="rId29" xr:uid="{DE4430AA-CCCA-43A8-AFC4-CE56FE18EA15}"/>
+    <hyperlink ref="Q34" r:id="rId30" xr:uid="{10C6B123-5519-4AD4-999A-7884D1DDFCDD}"/>
+    <hyperlink ref="Q35" r:id="rId31" xr:uid="{067B09F0-F1B7-4898-B09B-D5F7B5BC2A4F}"/>
+    <hyperlink ref="Q36" r:id="rId32" xr:uid="{5F6AEE85-684E-48FB-84BE-10E41ECFD008}"/>
+    <hyperlink ref="Q37" r:id="rId33" xr:uid="{A0419D12-FC02-4611-9947-11071E0C8178}"/>
+    <hyperlink ref="Q38" r:id="rId34" xr:uid="{70FCA407-AADC-4E6D-BA46-DB30BFB9252D}"/>
+    <hyperlink ref="Q39" r:id="rId35" xr:uid="{CA083B62-2DE3-4B7B-AD94-0C25C377617B}"/>
+    <hyperlink ref="Q40" r:id="rId36" xr:uid="{53800147-DB60-4841-9D4F-16EEA6AFCEC2}"/>
+    <hyperlink ref="Q41" r:id="rId37" xr:uid="{261D903B-6D6C-4255-B2EB-D6C458760ED6}"/>
+    <hyperlink ref="Q42" r:id="rId38" xr:uid="{176CFF0E-7C99-4934-8A59-A72C880B0499}"/>
+    <hyperlink ref="Q43" r:id="rId39" xr:uid="{52F57B38-A624-4422-8101-5277938001E9}"/>
+    <hyperlink ref="Q44" r:id="rId40" xr:uid="{22435A1F-6C7C-4F7B-887A-8F95CC844F65}"/>
+    <hyperlink ref="Q45" r:id="rId41" xr:uid="{2313E494-F71A-4817-82A8-04C2FC23FCD3}"/>
+    <hyperlink ref="Q46" r:id="rId42" xr:uid="{4FCC4804-3C51-4D5E-89E7-2CEEC4AEBDDF}"/>
+    <hyperlink ref="Q47" r:id="rId43" display="https://www.worldbank.org/content/dam/Worldbank/document/SAR/nepal/PDNA Volume A Final.pdf" xr:uid="{C16A0E7A-1F81-4F99-B0EB-24B0882E40B9}"/>
+    <hyperlink ref="Q48" r:id="rId44" xr:uid="{9D99DBDD-221C-49D4-9E55-7F20A3F2A7B1}"/>
+    <hyperlink ref="Q49" r:id="rId45" xr:uid="{DA41B2EB-C303-4E89-9D96-D443C427CC80}"/>
+    <hyperlink ref="Q50" r:id="rId46" xr:uid="{17D3D12D-3FE6-47B5-8863-F19B0E70BFC2}"/>
+    <hyperlink ref="Q51" r:id="rId47" xr:uid="{2DD8EAB9-0A02-4443-88A9-6394486EBC01}"/>
+    <hyperlink ref="Q52" r:id="rId48" xr:uid="{5B22EAA0-11FD-4DBF-9966-F599E9BD9FF1}"/>
+    <hyperlink ref="Q53" r:id="rId49" xr:uid="{3060A677-8AE4-48DD-9BF0-3F610F4A6F47}"/>
+    <hyperlink ref="Q54" r:id="rId50" xr:uid="{7D06B00E-D802-4CD9-A448-42825547189C}"/>
+    <hyperlink ref="Q55" r:id="rId51" xr:uid="{7797E73C-2D85-43B2-90CA-CDD133D18BA3}"/>
+    <hyperlink ref="Q56" r:id="rId52" xr:uid="{B8ABE114-85AD-4296-8D19-908827AA0DB5}"/>
+    <hyperlink ref="Q57" r:id="rId53" xr:uid="{71205EE2-33F4-4788-B16A-184BAFEB912D}"/>
+    <hyperlink ref="Q58" r:id="rId54" xr:uid="{645C3A94-8B94-40AD-A4EF-12B76EDAC785}"/>
+    <hyperlink ref="Q59" r:id="rId55" xr:uid="{D72A247F-5B19-4F2C-AF3A-D7EE211C8BD1}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3888888888888889" bottom="0.3888888888888889" header="0.3" footer="0.19444444444444445"/>
-  <pageSetup paperSize="9" scale="29" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId53"/>
+  <pageSetup paperSize="9" scale="29" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId56"/>
   <headerFooter>
     <oddFooter>&amp;CWorking draft | Evidence cutoff 31 July 2026 | Page &amp;P of &amp;N_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 INTERNAL. This information is accessible to ADB Management and Staff. It may be shared outside ADB with appropriate permission.</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId54"/>
+    <tablePart r:id="rId57"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39225756-889E-4B0C-B3E2-27B973B4EFE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28C9A9B8-6AB5-4D30-BC1B-BE4C8FDCB383}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7994,7 +8294,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>741</v>
+        <v>782</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8006,7 +8306,7 @@
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>742</v>
+        <v>783</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8033,13 +8333,13 @@
         <v>55</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>743</v>
+        <v>784</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>744</v>
+        <v>785</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
@@ -8450,21 +8750,21 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H5" r:id="rId1" xr:uid="{058858FE-AE0F-4B71-BDE7-D026A33CA2E6}"/>
-    <hyperlink ref="H6" r:id="rId2" xr:uid="{F2B7FF52-ECFB-4EF6-A1FA-F987CDDCE450}"/>
-    <hyperlink ref="H7" r:id="rId3" xr:uid="{D7524D51-F811-4DEF-80E9-C84C7859458F}"/>
-    <hyperlink ref="H8" r:id="rId4" xr:uid="{C17E6CCF-A130-48A6-9BA9-42010644A879}"/>
-    <hyperlink ref="H9" r:id="rId5" xr:uid="{90F8FDB9-AA69-4787-AD50-EF529650A996}"/>
-    <hyperlink ref="H10" r:id="rId6" xr:uid="{8E61A8DF-478B-442A-8116-2579174BF9FE}"/>
-    <hyperlink ref="H11" r:id="rId7" xr:uid="{569CB69D-9226-4EE2-9456-6B19CF230C7F}"/>
-    <hyperlink ref="H12" r:id="rId8" xr:uid="{3B3734C4-5817-49D3-9989-478CA2C8575F}"/>
-    <hyperlink ref="H13" r:id="rId9" xr:uid="{C526A031-FF30-4601-AA6C-A49DCBB095BE}"/>
-    <hyperlink ref="H14" r:id="rId10" xr:uid="{11DC8EDD-9246-46F2-BB8A-587B9BE30C37}"/>
-    <hyperlink ref="H15" r:id="rId11" xr:uid="{A4C4922E-D905-467F-83C7-60A854416B4A}"/>
-    <hyperlink ref="H16" r:id="rId12" xr:uid="{97A04386-29FD-4B76-9245-405294B58A2B}"/>
-    <hyperlink ref="H17" r:id="rId13" xr:uid="{2D91FB03-69D3-458D-B330-56931EBB4216}"/>
-    <hyperlink ref="H18" r:id="rId14" xr:uid="{00B0EBD9-194B-4AFD-AAB3-D35B2FFFCEAD}"/>
-    <hyperlink ref="H19" r:id="rId15" xr:uid="{A2503E8C-88EE-4633-97C3-68FF6A8080B5}"/>
+    <hyperlink ref="H5" r:id="rId1" xr:uid="{BD63353B-40B2-43F0-AE91-839DA09EDA73}"/>
+    <hyperlink ref="H6" r:id="rId2" xr:uid="{D169EFD4-A307-4EBD-A72C-B1C0394EC177}"/>
+    <hyperlink ref="H7" r:id="rId3" xr:uid="{09009A9C-E20D-4E35-AC7B-623D459F132F}"/>
+    <hyperlink ref="H8" r:id="rId4" xr:uid="{8F1B8076-97D6-4167-8C0E-620703A4BE12}"/>
+    <hyperlink ref="H9" r:id="rId5" xr:uid="{FE64AB5F-CA3C-4987-846D-74B626EE05D6}"/>
+    <hyperlink ref="H10" r:id="rId6" xr:uid="{BEDEC184-4568-4FD5-AD7D-0FACC89200C6}"/>
+    <hyperlink ref="H11" r:id="rId7" xr:uid="{5DE08377-168C-41C9-A188-D9210224D9F8}"/>
+    <hyperlink ref="H12" r:id="rId8" xr:uid="{386D7304-9E30-4F95-95EA-0FEC3D7BB713}"/>
+    <hyperlink ref="H13" r:id="rId9" xr:uid="{4285921B-D0C2-4411-A65F-C34880BFED43}"/>
+    <hyperlink ref="H14" r:id="rId10" xr:uid="{5D29F03B-46E7-4B5A-B8A8-3A397160649D}"/>
+    <hyperlink ref="H15" r:id="rId11" xr:uid="{DE82A2F1-3EC2-498F-84A7-93E723616E2C}"/>
+    <hyperlink ref="H16" r:id="rId12" xr:uid="{5EEB6225-CEA0-4DB7-A113-27C43C163392}"/>
+    <hyperlink ref="H17" r:id="rId13" xr:uid="{43A25F84-30B3-4DDE-AC4F-DB59E84CCC22}"/>
+    <hyperlink ref="H18" r:id="rId14" xr:uid="{3794126C-6142-400A-9245-A649E34A74F1}"/>
+    <hyperlink ref="H19" r:id="rId15" xr:uid="{94325608-B1BE-45D7-874B-C607FE9AB801}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3888888888888889" bottom="0.3888888888888889" header="0.3" footer="0.19444444444444445"/>
@@ -8476,7 +8776,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9617BB79-3429-444F-B289-FCF5C5CFC380}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB75753C-BB93-4A95-8361-DE1055931DBA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8494,7 +8794,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>745</v>
+        <v>786</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8504,7 +8804,7 @@
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>746</v>
+        <v>787</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8514,22 +8814,22 @@
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>747</v>
+        <v>788</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>748</v>
+        <v>789</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>749</v>
+        <v>790</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>751</v>
+        <v>792</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8537,19 +8837,19 @@
         <v>254</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>752</v>
+        <v>793</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>753</v>
+        <v>794</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>754</v>
+        <v>795</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>755</v>
+        <v>796</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>756</v>
+        <v>797</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8557,19 +8857,19 @@
         <v>75</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>757</v>
+        <v>798</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>758</v>
+        <v>799</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>759</v>
+        <v>800</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>760</v>
+        <v>801</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>761</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8577,19 +8877,19 @@
         <v>384</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>762</v>
+        <v>803</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>763</v>
+        <v>804</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>764</v>
+        <v>805</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>765</v>
+        <v>806</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>766</v>
+        <v>807</v>
       </c>
     </row>
   </sheetData>
@@ -8607,7 +8907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193E4497-C0D4-495C-8041-7829F47D3394}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C47CA43B-4756-4893-943B-1D3896372213}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8622,7 +8922,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>767</v>
+        <v>808</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8634,7 +8934,7 @@
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>768</v>
+        <v>809</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8646,259 +8946,259 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="26" t="s">
-        <v>769</v>
+        <v>810</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>770</v>
+        <v>811</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>771</v>
+        <v>812</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>772</v>
+        <v>813</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="27" t="s">
-        <v>773</v>
+        <v>814</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>774</v>
+        <v>815</v>
       </c>
       <c r="C5" s="28">
         <v>2</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>775</v>
+        <v>816</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="27" t="s">
-        <v>773</v>
+        <v>814</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>776</v>
+        <v>817</v>
       </c>
       <c r="C6" s="28">
         <v>7.75</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>777</v>
+        <v>818</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
-        <v>773</v>
+        <v>814</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>778</v>
+        <v>819</v>
       </c>
       <c r="C7" s="28">
         <v>11</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>775</v>
+        <v>816</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
-        <v>773</v>
+        <v>814</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>779</v>
+        <v>820</v>
       </c>
       <c r="C8" s="28">
         <v>11.9</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>780</v>
+        <v>821</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>782</v>
+        <v>823</v>
       </c>
       <c r="C9" s="28">
         <v>81</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>783</v>
+        <v>824</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="27" t="s">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>784</v>
+        <v>825</v>
       </c>
       <c r="C10" s="28">
         <v>77.5</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>785</v>
+        <v>826</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="27" t="s">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>786</v>
+        <v>827</v>
       </c>
       <c r="C11" s="28">
         <v>8.75</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>785</v>
+        <v>826</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>787</v>
+        <v>828</v>
       </c>
       <c r="C12" s="28">
         <v>4.07</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>788</v>
+        <v>829</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="27" t="s">
-        <v>789</v>
+        <v>830</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>790</v>
+        <v>831</v>
       </c>
       <c r="C13" s="28">
         <v>3.8</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>775</v>
+        <v>816</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
-        <v>789</v>
+        <v>830</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>791</v>
+        <v>832</v>
       </c>
       <c r="C14" s="28">
         <v>14.4</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>775</v>
+        <v>816</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="27" t="s">
-        <v>789</v>
+        <v>830</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>792</v>
+        <v>833</v>
       </c>
       <c r="C15" s="28">
         <v>18</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>780</v>
+        <v>821</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="27" t="s">
-        <v>789</v>
+        <v>830</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>793</v>
+        <v>834</v>
       </c>
       <c r="C16" s="28">
         <v>9</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>794</v>
+        <v>835</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="27" t="s">
-        <v>795</v>
+        <v>836</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>796</v>
+        <v>837</v>
       </c>
       <c r="C17" s="28">
         <v>18.5</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>797</v>
+        <v>838</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="27" t="s">
-        <v>795</v>
+        <v>836</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>798</v>
+        <v>839</v>
       </c>
       <c r="C18" s="28">
         <v>31</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>797</v>
+        <v>838</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="27" t="s">
-        <v>795</v>
+        <v>836</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>799</v>
+        <v>840</v>
       </c>
       <c r="C19" s="28">
         <v>64</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>797</v>
+        <v>838</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="27" t="s">
-        <v>795</v>
+        <v>836</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="C20" s="28">
         <v>41</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>801</v>
+        <v>842</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>802</v>
+        <v>843</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>804</v>
+        <v>845</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>805</v>
+        <v>846</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>806</v>
+        <v>847</v>
       </c>
       <c r="B24" s="5">
         <v>1</v>
@@ -8912,7 +9212,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>807</v>
+        <v>848</v>
       </c>
       <c r="B25" s="5">
         <v>2</v>
@@ -8926,7 +9226,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>808</v>
+        <v>849</v>
       </c>
       <c r="B26" s="5">
         <v>3</v>
@@ -8940,7 +9240,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>809</v>
+        <v>850</v>
       </c>
       <c r="B27" s="5">
         <v>3</v>
@@ -8954,7 +9254,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>810</v>
+        <v>851</v>
       </c>
       <c r="B28" s="5">
         <v>2</v>
@@ -8968,7 +9268,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>811</v>
+        <v>852</v>
       </c>
       <c r="B29" s="5">
         <v>2</v>
@@ -8982,7 +9282,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="29" t="s">
-        <v>812</v>
+        <v>853</v>
       </c>
       <c r="B30" s="5">
         <v>3</v>
@@ -8996,10 +9296,10 @@
     </row>
     <row r="34" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>813</v>
+        <v>854</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>814</v>
+        <v>855</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -9023,12 +9323,12 @@
         <v>157</v>
       </c>
       <c r="B37" s="5">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>815</v>
+        <v>856</v>
       </c>
       <c r="B38" s="5">
         <v>5</v>
@@ -9057,7 +9357,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09EDB23-9F10-457D-87EF-1D4A2C720395}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E6C523-A4B2-46E2-B078-F2D6F5A25AA0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -9074,7 +9374,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>816</v>
+        <v>857</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9083,7 +9383,7 @@
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9092,104 +9392,104 @@
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>818</v>
+        <v>859</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>819</v>
+        <v>860</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>820</v>
+        <v>861</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>821</v>
+        <v>862</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>822</v>
+        <v>863</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>823</v>
+        <v>864</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>824</v>
+        <v>865</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>825</v>
+        <v>866</v>
       </c>
       <c r="D5" s="8">
         <v>46238</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>826</v>
+        <v>867</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>827</v>
+        <v>868</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>828</v>
+        <v>869</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>829</v>
+        <v>870</v>
       </c>
       <c r="D6" s="8">
         <v>46238</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>830</v>
+        <v>871</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>831</v>
+        <v>872</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>832</v>
+        <v>873</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>833</v>
+        <v>874</v>
       </c>
       <c r="D7" s="8">
         <v>46238</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>834</v>
+        <v>875</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>835</v>
+        <v>876</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>836</v>
+        <v>877</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>837</v>
+        <v>878</v>
       </c>
       <c r="D8" s="8">
         <v>46238</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>838</v>
+        <v>879</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>839</v>
+        <v>880</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>840</v>
+        <v>881</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>841</v>
+        <v>882</v>
       </c>
       <c r="D9" s="8">
         <v>46238</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>842</v>
+        <v>883</v>
       </c>
     </row>
   </sheetData>
@@ -9207,11 +9507,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3B3F86-769E-4DB6-806B-78303D0CCD02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7607B8A-B629-46C6-9792-1315A0B23624}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -9222,27 +9522,27 @@
   <sheetData>
     <row r="1" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>843</v>
+        <v>884</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>844</v>
+        <v>885</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>845</v>
+        <v>886</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>846</v>
+        <v>887</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>847</v>
+        <v>888</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9250,10 +9550,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>848</v>
+        <v>889</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9261,10 +9561,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>850</v>
+        <v>891</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9272,10 +9572,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>851</v>
+        <v>892</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9283,10 +9583,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>852</v>
+        <v>893</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9294,10 +9594,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>853</v>
+        <v>894</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9305,10 +9605,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>854</v>
+        <v>895</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9316,10 +9616,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>855</v>
+        <v>896</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9327,10 +9627,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>856</v>
+        <v>897</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9338,10 +9638,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>857</v>
+        <v>898</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9349,10 +9649,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>858</v>
+        <v>899</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9360,10 +9660,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>859</v>
+        <v>900</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9371,10 +9671,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>860</v>
+        <v>901</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9382,10 +9682,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>861</v>
+        <v>902</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9393,10 +9693,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>862</v>
+        <v>903</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9404,10 +9704,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>863</v>
+        <v>904</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9415,10 +9715,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>864</v>
+        <v>905</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9426,10 +9726,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>865</v>
+        <v>906</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9437,10 +9737,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>866</v>
+        <v>907</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9448,10 +9748,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>867</v>
+        <v>908</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9459,10 +9759,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>868</v>
+        <v>909</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9470,10 +9770,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>869</v>
+        <v>910</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9481,10 +9781,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>870</v>
+        <v>911</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9492,10 +9792,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>871</v>
+        <v>912</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9503,10 +9803,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>872</v>
+        <v>913</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9514,10 +9814,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>873</v>
+        <v>914</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9525,10 +9825,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>874</v>
+        <v>915</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9536,10 +9836,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>875</v>
+        <v>916</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9547,10 +9847,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>876</v>
+        <v>917</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9558,10 +9858,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>877</v>
+        <v>918</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9569,10 +9869,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>878</v>
+        <v>919</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9580,10 +9880,10 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>879</v>
+        <v>920</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9591,10 +9891,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>880</v>
+        <v>921</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9602,10 +9902,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>881</v>
+        <v>922</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9613,10 +9913,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>882</v>
+        <v>923</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9624,10 +9924,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>883</v>
+        <v>924</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9635,10 +9935,10 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>884</v>
+        <v>925</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9646,10 +9946,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>885</v>
+        <v>926</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9657,10 +9957,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>886</v>
+        <v>927</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9668,10 +9968,10 @@
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>887</v>
+        <v>928</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9679,10 +9979,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>888</v>
+        <v>929</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9690,10 +9990,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>889</v>
+        <v>930</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9701,10 +10001,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
+        <v>931</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>890</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9712,10 +10012,10 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>891</v>
+        <v>932</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9723,10 +10023,10 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>892</v>
+        <v>933</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9734,10 +10034,10 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>893</v>
+        <v>934</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9745,10 +10045,10 @@
         <v>46</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>894</v>
+        <v>935</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9756,10 +10056,10 @@
         <v>47</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>895</v>
+        <v>936</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9767,10 +10067,10 @@
         <v>48</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>896</v>
+        <v>937</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9778,10 +10078,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>897</v>
+        <v>938</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9789,10 +10089,10 @@
         <v>50</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>898</v>
+        <v>939</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9800,10 +10100,10 @@
         <v>51</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>899</v>
+        <v>940</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9811,10 +10111,10 @@
         <v>52</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>900</v>
+        <v>941</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9822,10 +10122,10 @@
         <v>53</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>901</v>
+        <v>942</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9833,10 +10133,10 @@
         <v>54</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>902</v>
+        <v>943</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9844,10 +10144,32 @@
         <v>55</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>903</v>
+        <v>944</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>849</v>
+        <v>890</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="7">
+        <v>56</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>945</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="7">
+        <v>57</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>946</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>890</v>
       </c>
     </row>
   </sheetData>

--- a/reporting-site/public/reviews/task31/artifacts/Asia_Pacific_Welfare_Losses_Evidence_Register_2026.xlsx
+++ b/reporting-site/public/reviews/task31/artifacts/Asia_Pacific_Welfare_Losses_Evidence_Register_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Raymond\OneDrive\Desktop\ADB\Research\Task31\outputs\task31_welfare_review_20260804\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A77F126B-6ADF-4C24-969D-CFE69000CF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC94F239-2062-450C-97D5-97358BF48550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1380" windowWidth="4365" windowHeight="2820" xr2:uid="{71789420-CE43-49EA-80AF-055733162645}"/>
+    <workbookView xWindow="1380" yWindow="1380" windowWidth="4365" windowHeight="2820" xr2:uid="{FEA55C93-3789-4855-8005-8D0F3D741507}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,11 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Confidence Rubric'!$A$1:$F$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Dashboard!$A$1:$K$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Evidence!$A$1:$R$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Evidence!$A$1:$R$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Figure Data'!$A$1:$D$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Key Estimates'!$A$1:$H$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">README!$A$1:$F$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">References!$A$1:$C$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">References!$A$1:$C$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Search Log'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="1000">
   <si>
     <t>Welfare losses evidence register</t>
   </si>
@@ -2404,6 +2404,84 @@
     <t>10.1086/713939</t>
   </si>
   <si>
+    <t>E13</t>
+  </si>
+  <si>
+    <t>Seitz (2019)</t>
+  </si>
+  <si>
+    <t>World Bank, International Migration and Household Well-Being: Evidence from Uzbekistan</t>
+  </si>
+  <si>
+    <t>Uzbekistan</t>
+  </si>
+  <si>
+    <t>Households with and without international migrants</t>
+  </si>
+  <si>
+    <t>Weak local labour markets and dependence on migration income</t>
+  </si>
+  <si>
+    <t>Poverty, household income composition, and subjective wellbeing</t>
+  </si>
+  <si>
+    <t>Remittances account for 11% of household income in the poorest quintile and about 8% in the richest; removing remittance income from consumption raises the poverty rate 7.2 percentage points, from 9.6% to 16.8%, and even if every migrant returned and earned their home-province median wage the rate would still rise 2.6 points</t>
+  </si>
+  <si>
+    <t>Panel survey (Listening to the Citizens of Uzbekistan) linked to administrative records, with counterfactual poverty simulation</t>
+  </si>
+  <si>
+    <t>Household panel with fixed effects for time-invariant respondent and location characteristics; the poverty figures are simulated counterfactuals, not observed outcomes</t>
+  </si>
+  <si>
+    <t>The counterfactual removes remittances without allowing labour-market or price adjustment, so it bounds rather than estimates the effect. The migration decision is not exogenous, though the panel controls for fixed unobservables</t>
+  </si>
+  <si>
+    <t>Household panel with counterfactual simulation</t>
+  </si>
+  <si>
+    <t>https://documents.worldbank.org/curated/en/902731561151905908/pdf/International-Migration-and-Household-Well-Being-Evidence-from-Uzbekistan.pdf</t>
+  </si>
+  <si>
+    <t>E14</t>
+  </si>
+  <si>
+    <t>World Bank (2015)</t>
+  </si>
+  <si>
+    <t>Kyrgyz Republic Economic Update: Adjusting to a Challenging Regional Economic Environment</t>
+  </si>
+  <si>
+    <t>Kyrgyz Republic</t>
+  </si>
+  <si>
+    <t>Remittance-receiving households and the wider economy</t>
+  </si>
+  <si>
+    <t>Regional slowdown transmitted through migrant labour demand and remittances</t>
+  </si>
+  <si>
+    <t>Remittance income, transfers, growth, and poverty</t>
+  </si>
+  <si>
+    <t>Remittances fell 3% year-on-year in dollar terms in 2014 after growing 8% in 2013, and lower remittances more than offset higher public grants, cutting transfers from 31% of GDP in 2013 to 29.1%; growth was projected to fall to 1.7% in 2015 against national absolute poverty of 37.0% in 2013</t>
+  </si>
+  <si>
+    <t>Country economic update combining national accounts, balance-of-payments, and household poverty statistics</t>
+  </si>
+  <si>
+    <t>Observed macro deterioration attributed to a regional shock; no counterfactual decomposition</t>
+  </si>
+  <si>
+    <t>The remittance decline is partly an exchange-rate effect rather than a volume effect, which the source states explicitly; poverty is a 2013 baseline and not a post-shock measurement, so this record documents transmission rather than a realised welfare loss</t>
+  </si>
+  <si>
+    <t>Country macro-poverty update</t>
+  </si>
+  <si>
+    <t>https://documents.worldbank.org/curated/en/741101611290294918/pdf/Kyrgyz-Republic-Economic-Update-Adjusting-to-a-Challenging-Regional-Economic-Environment.pdf</t>
+  </si>
+  <si>
     <t>Key quantitative estimates</t>
   </si>
   <si>
@@ -2897,6 +2975,12 @@
   </si>
   <si>
     <t>Tiwari, S., Jacoby, H. G., and Skoufias, E. (2016). Monsoon Babies: Rainfall Shocks and Child Nutrition in Nepal. Economic Development and Cultural Change. https://doi.org/10.1086/689308</t>
+  </si>
+  <si>
+    <t>Seitz, W. (2019). International Migration and Household Well-Being: Evidence from Uzbekistan. Policy Research Working Paper. World Bank. https://documents.worldbank.org/curated/en/902731561151905908</t>
+  </si>
+  <si>
+    <t>World Bank (2015). Kyrgyz Republic Economic Update: Adjusting to a Challenging Regional Economic Environment. https://documents.worldbank.org/curated/en/741101611290294918</t>
   </si>
   <si>
     <t>Asia-Pacific welfare-loss evidence dashboard</t>
@@ -4107,7 +4191,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>27</c:v>
@@ -4117,7 +4201,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-CA05-423B-9B88-40E07BC0BCDC}"/>
+              <c16:uniqueId val="{00000002-194D-4337-A9C8-E1DEDBE15C63}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4130,11 +4214,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="937892144"/>
-        <c:axId val="937893104"/>
+        <c:axId val="706059936"/>
+        <c:axId val="706071936"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="937892144"/>
+        <c:axId val="706059936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4144,7 +4228,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="937893104"/>
+        <c:crossAx val="706071936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4152,7 +4236,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="937893104"/>
+        <c:axId val="706071936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4163,7 +4247,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="937892144"/>
+        <c:crossAx val="706059936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4231,7 +4315,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2CFC370-9F6C-9EA3-0AC6-EF9AE6B30D8E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09BE01AE-4EEA-23AE-0201-20B6D469CF88}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4253,27 +4337,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E926FF29-EACA-4636-8A32-D714EC331C99}" name="EvidenceTable" displayName="EvidenceTable" ref="A4:R59" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
-  <autoFilter ref="A4:R59" xr:uid="{E926FF29-EACA-4636-8A32-D714EC331C99}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2438F6B0-4674-444B-9641-6F0D472089B6}" name="EvidenceTable" displayName="EvidenceTable" ref="A4:R61" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+  <autoFilter ref="A4:R61" xr:uid="{2438F6B0-4674-444B-9641-6F0D472089B6}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{A699042E-9D55-4AF1-93C4-CFD67498F039}" name="ID" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{A3CE8752-D3C4-4B63-9E52-86D68C417CF8}" name="Category" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{6A49B28E-7D87-42B8-ADD2-940331B8D64B}" name="Study" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{9B57F65E-FF1F-41EC-BAC6-789FFF264C0C}" name="Year" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{E4579502-C6BD-4579-AD93-E6C79059A575}" name="Source" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{D9ED3A83-6150-4BA2-87BD-E3DD7D5F756F}" name="Geography" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{3BD187C6-D8FC-40CA-B5C8-A02E4C297FA2}" name="Subregion" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{2F4507CD-015F-4DDD-B80C-80490A575C52}" name="Population" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{72EFC807-A691-4279-ABAF-C70E1C6C4D93}" name="Shock" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{969425AB-FFE5-4745-89F8-A719AE03B156}" name="Welfare Indicator" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{89FD63C1-3465-4FA6-BC72-360C2D3A5208}" name="Estimate" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{E723DB08-915D-4647-98D7-E2B5E8EC3A0B}" name="Methodology" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{54457B76-FBFB-44BE-90B9-A3D7E887C66A}" name="Identification" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{C848C2E3-3E3F-4196-9C94-60DC27CF46C2}" name="Limitations" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{5237D108-D0B1-46BB-B2C8-50C6C49F648A}" name="Confidence" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{ADD5CFFA-D18C-415E-955B-2A6D61AF0AF5}" name="Evidence Type" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{6D088BA7-2F4E-46C4-9B96-E4E3350FC88A}" name="URL" dataDxfId="0"/>
-    <tableColumn id="18" xr3:uid="{7E6AAADA-EF8C-4F1B-9398-B6155AC0D935}" name="DOI" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{97C0429A-6540-41C2-876F-24081354CC65}" name="ID" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{ED59F510-5403-4C1C-B9BC-F5B128D4088B}" name="Category" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{FD91F0BB-485B-46B8-8C65-93ECEF6BF8CC}" name="Study" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{43CF9281-56CC-4A90-856E-51E7B7E3123A}" name="Year" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{E14EC942-BDCC-4D85-95B3-B88A057A9C54}" name="Source" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{9D82D25A-9AFA-45B3-937F-EA0B205F5EC5}" name="Geography" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{99F29E18-16E9-4420-B169-FB984D7B20F0}" name="Subregion" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{956409FC-5053-49AD-9317-ADF1C43D38AD}" name="Population" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{E8A6A0FF-119D-4909-957F-83AD1C765E95}" name="Shock" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{0CD1E7D6-2875-4B23-A315-28DD3BD6DEDA}" name="Welfare Indicator" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{BC1E52D1-5E8D-4738-9582-3790244A395D}" name="Estimate" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{9366D95C-685B-4097-BBAB-0484CEAB263A}" name="Methodology" dataDxfId="11"/>
+    <tableColumn id="13" xr3:uid="{B5C2AFF3-7ABD-4D16-97EA-1A70E7DD62A9}" name="Identification" dataDxfId="10"/>
+    <tableColumn id="14" xr3:uid="{BE3F7129-2872-446F-8FE5-824A258CE7BF}" name="Limitations" dataDxfId="9"/>
+    <tableColumn id="15" xr3:uid="{5B842671-3B59-4592-ADDE-0BD3D367F5AF}" name="Confidence" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{1ACA4076-36D7-4830-95FC-1529636455A4}" name="Evidence Type" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{0A76A483-5590-4A90-BAEF-E180290F035E}" name="URL" dataDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{8EE1F0F8-7F8B-424C-9B69-5281FB752DBE}" name="DOI" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4595,7 +4679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5883C86C-13C3-435E-A556-E4D508D3F2C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ADF8D07-C9BA-4686-822D-CF07BF91EFCD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4614,7 +4698,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>947</v>
+        <v>975</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4629,7 +4713,7 @@
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>948</v>
+        <v>976</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4644,7 +4728,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="30" t="s">
-        <v>949</v>
+        <v>977</v>
       </c>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -4659,87 +4743,87 @@
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
-        <v>950</v>
+        <v>978</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>812</v>
+        <v>838</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>951</v>
+        <v>979</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
-        <v>952</v>
+        <v>980</v>
       </c>
       <c r="B7" s="31">
         <f>ROWS(EvidenceTable[ID])</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>953</v>
+        <v>981</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
-        <v>954</v>
+        <v>982</v>
       </c>
       <c r="B8" s="31">
         <f>COUNTIF(EvidenceTable[Source],"*Journal*")+COUNTIF(EvidenceTable[Source],"Nature*")+COUNTIF(EvidenceTable[Source],"Science*")+COUNTIF(EvidenceTable[Source],"The Lancet*")+COUNTIF(EvidenceTable[Source],"Proceedings*")+COUNTIF(EvidenceTable[Source],"World Development")+COUNTIF(EvidenceTable[Source],"Quarterly*")</f>
         <v>23</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>955</v>
+        <v>983</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
-        <v>956</v>
+        <v>984</v>
       </c>
       <c r="B9" s="31">
         <f>COUNTIF(EvidenceTable[Confidence],"High")</f>
         <v>20</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>957</v>
+        <v>985</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="27" t="s">
-        <v>958</v>
+        <v>986</v>
       </c>
       <c r="B10" s="31">
         <f>COUNTIF(EvidenceTable[Confidence],"Medium")</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>959</v>
+        <v>987</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="27" t="s">
-        <v>960</v>
+        <v>988</v>
       </c>
       <c r="B11" s="31">
         <f>COUNTIF(EvidenceTable[Confidence],"Low")</f>
         <v>1</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>961</v>
+        <v>989</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="26" t="s">
-        <v>962</v>
+        <v>990</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>952</v>
+        <v>980</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>952</v>
+        <v>980</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -4764,14 +4848,14 @@
       </c>
       <c r="B15" s="33">
         <f>COUNTIF(EvidenceTable[Category],A15)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E15" s="32" t="s">
         <v>75</v>
       </c>
       <c r="F15" s="32">
         <f>COUNTIF(EvidenceTable[Confidence],E15)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -4792,7 +4876,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="34" t="s">
-        <v>963</v>
+        <v>991</v>
       </c>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -4807,34 +4891,34 @@
     </row>
     <row r="20" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="35" t="s">
-        <v>964</v>
+        <v>992</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>965</v>
+        <v>993</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="35" t="s">
-        <v>966</v>
+        <v>994</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>967</v>
+        <v>995</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
-        <v>968</v>
+        <v>996</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>969</v>
+        <v>997</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="35" t="s">
-        <v>970</v>
+        <v>998</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>971</v>
+        <v>999</v>
       </c>
     </row>
   </sheetData>
@@ -4855,7 +4939,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF7550D6-A9D0-485A-BA5D-69CFBEA62F92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFEC6B0B-5BA6-4B91-B795-47C753DF4BA1}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5046,11 +5130,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B95C6F-0A6E-4880-B572-E0B0962604DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{141375EE-80AC-41C6-B741-6EC6E143093B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R59"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -8139,60 +8223,168 @@
       </c>
     </row>
     <row r="59" spans="1:18" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="11" t="s">
         <v>769</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="C59" s="17" t="s">
+      <c r="C59" s="10" t="s">
         <v>770</v>
       </c>
-      <c r="D59" s="20">
+      <c r="D59" s="19">
         <v>2021</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="F59" s="10" t="s">
         <v>771</v>
       </c>
-      <c r="G59" s="17" t="s">
+      <c r="G59" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="H59" s="17" t="s">
+      <c r="H59" s="10" t="s">
         <v>772</v>
       </c>
-      <c r="I59" s="17" t="s">
+      <c r="I59" s="10" t="s">
         <v>773</v>
       </c>
-      <c r="J59" s="17" t="s">
+      <c r="J59" s="10" t="s">
         <v>774</v>
       </c>
-      <c r="K59" s="17" t="s">
+      <c r="K59" s="10" t="s">
         <v>775</v>
       </c>
-      <c r="L59" s="17" t="s">
+      <c r="L59" s="10" t="s">
         <v>776</v>
       </c>
-      <c r="M59" s="17" t="s">
+      <c r="M59" s="10" t="s">
         <v>777</v>
       </c>
-      <c r="N59" s="17" t="s">
+      <c r="N59" s="10" t="s">
         <v>778</v>
       </c>
-      <c r="O59" s="17" t="s">
+      <c r="O59" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="P59" s="17" t="s">
+      <c r="P59" s="10" t="s">
         <v>779</v>
       </c>
-      <c r="Q59" s="22" t="s">
+      <c r="Q59" s="21" t="s">
         <v>780</v>
       </c>
-      <c r="R59" s="18" t="s">
+      <c r="R59" s="12" t="s">
         <v>781</v>
       </c>
+    </row>
+    <row r="60" spans="1:18" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="D60" s="19">
+        <v>2019</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>784</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>785</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>786</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>787</v>
+      </c>
+      <c r="J60" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>789</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>790</v>
+      </c>
+      <c r="M60" s="10" t="s">
+        <v>791</v>
+      </c>
+      <c r="N60" s="10" t="s">
+        <v>792</v>
+      </c>
+      <c r="O60" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="P60" s="10" t="s">
+        <v>793</v>
+      </c>
+      <c r="Q60" s="21" t="s">
+        <v>794</v>
+      </c>
+      <c r="R60" s="12"/>
+    </row>
+    <row r="61" spans="1:18" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="D61" s="20">
+        <v>2015</v>
+      </c>
+      <c r="E61" s="17" t="s">
+        <v>797</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>798</v>
+      </c>
+      <c r="G61" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="H61" s="17" t="s">
+        <v>799</v>
+      </c>
+      <c r="I61" s="17" t="s">
+        <v>800</v>
+      </c>
+      <c r="J61" s="17" t="s">
+        <v>801</v>
+      </c>
+      <c r="K61" s="17" t="s">
+        <v>802</v>
+      </c>
+      <c r="L61" s="17" t="s">
+        <v>803</v>
+      </c>
+      <c r="M61" s="17" t="s">
+        <v>804</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>805</v>
+      </c>
+      <c r="O61" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="P61" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="Q61" s="22" t="s">
+        <v>807</v>
+      </c>
+      <c r="R61" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8200,81 +8392,83 @@
     <mergeCell ref="A2:R2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5:O59" xr:uid="{7B1CBE2F-C370-41C1-812B-91D9D2E9D815}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5:O61" xr:uid="{1B05F482-821D-4A24-820A-5ABE7894029B}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="Q5" r:id="rId1" xr:uid="{DF1031D9-0E5D-4543-9C35-54452D37ACD8}"/>
-    <hyperlink ref="Q6" r:id="rId2" xr:uid="{2811470A-28F0-4D9E-849D-5775F77F66A8}"/>
-    <hyperlink ref="Q7" r:id="rId3" xr:uid="{E739AE59-D03D-470B-91A6-6461D9FD142C}"/>
-    <hyperlink ref="Q8" r:id="rId4" xr:uid="{49CDD9AD-C0F4-450E-9B6E-8A5898FF7188}"/>
-    <hyperlink ref="Q9" r:id="rId5" xr:uid="{771B75F8-39E3-4B86-AE84-D52D56C53B8A}"/>
-    <hyperlink ref="Q10" r:id="rId6" xr:uid="{4C6864CB-0562-4C54-AA29-6DE85FBB1E63}"/>
-    <hyperlink ref="Q11" r:id="rId7" xr:uid="{ECFFAE5A-4184-4DBD-B753-F469FFE000CD}"/>
-    <hyperlink ref="Q12" r:id="rId8" xr:uid="{0BE39899-448C-46CD-A7AA-5018066D7F33}"/>
-    <hyperlink ref="Q13" r:id="rId9" xr:uid="{FCC18E01-6686-465B-82A1-AC4DE1F37931}"/>
-    <hyperlink ref="Q14" r:id="rId10" xr:uid="{3B01E7BC-D1BD-4DD7-B1E2-932738345E3C}"/>
-    <hyperlink ref="Q15" r:id="rId11" xr:uid="{D812DF4E-AE49-4F70-8418-F992D8888A9D}"/>
-    <hyperlink ref="Q16" r:id="rId12" xr:uid="{264F4447-3340-4052-83AA-3DB26CE8C7AD}"/>
-    <hyperlink ref="Q17" r:id="rId13" xr:uid="{170ADB16-52B8-4188-9649-CF35C9FE6054}"/>
-    <hyperlink ref="Q18" r:id="rId14" xr:uid="{DE3D0780-70AC-461C-A3C1-F5B11E42D3B7}"/>
-    <hyperlink ref="Q19" r:id="rId15" xr:uid="{4068BA23-4B41-440F-9645-91A7677F34EF}"/>
-    <hyperlink ref="Q20" r:id="rId16" xr:uid="{F51DC8B1-CE3C-42F6-B7AE-C832242897D3}"/>
-    <hyperlink ref="Q21" r:id="rId17" xr:uid="{FFD66CDE-E08F-466B-96B7-DA44D5FBD792}"/>
-    <hyperlink ref="Q22" r:id="rId18" xr:uid="{AD1EBEB8-DE23-420C-B724-99F1293E0206}"/>
-    <hyperlink ref="Q23" r:id="rId19" xr:uid="{43EFB4FC-7632-4272-A18F-FB614351A30F}"/>
-    <hyperlink ref="Q24" r:id="rId20" xr:uid="{01F6C2F6-7EE5-4A55-A38F-6162C02E3B83}"/>
-    <hyperlink ref="Q25" r:id="rId21" xr:uid="{7343D18A-EE7D-4CBC-93BD-F085EAA3AA60}"/>
-    <hyperlink ref="Q26" r:id="rId22" xr:uid="{C6C10368-89E2-4D29-9546-4225155EF8EF}"/>
-    <hyperlink ref="Q27" r:id="rId23" xr:uid="{B8BB4A4F-8068-4D74-8E41-CC356D357BBC}"/>
-    <hyperlink ref="Q28" r:id="rId24" xr:uid="{0C8109AD-50ED-4CED-88C6-73C023E442D3}"/>
-    <hyperlink ref="Q29" r:id="rId25" xr:uid="{C4A06113-FFBA-4EB7-B540-34F264D79676}"/>
-    <hyperlink ref="Q30" r:id="rId26" xr:uid="{5CC8C8C3-4895-4061-AFC7-5C078B460889}"/>
-    <hyperlink ref="Q31" r:id="rId27" xr:uid="{FCCB952C-D9EF-49ED-9647-DD3BAD1656C3}"/>
-    <hyperlink ref="Q32" r:id="rId28" xr:uid="{9032671A-FE70-433B-B3C6-D7FCAA1F7803}"/>
-    <hyperlink ref="Q33" r:id="rId29" xr:uid="{DE4430AA-CCCA-43A8-AFC4-CE56FE18EA15}"/>
-    <hyperlink ref="Q34" r:id="rId30" xr:uid="{10C6B123-5519-4AD4-999A-7884D1DDFCDD}"/>
-    <hyperlink ref="Q35" r:id="rId31" xr:uid="{067B09F0-F1B7-4898-B09B-D5F7B5BC2A4F}"/>
-    <hyperlink ref="Q36" r:id="rId32" xr:uid="{5F6AEE85-684E-48FB-84BE-10E41ECFD008}"/>
-    <hyperlink ref="Q37" r:id="rId33" xr:uid="{A0419D12-FC02-4611-9947-11071E0C8178}"/>
-    <hyperlink ref="Q38" r:id="rId34" xr:uid="{70FCA407-AADC-4E6D-BA46-DB30BFB9252D}"/>
-    <hyperlink ref="Q39" r:id="rId35" xr:uid="{CA083B62-2DE3-4B7B-AD94-0C25C377617B}"/>
-    <hyperlink ref="Q40" r:id="rId36" xr:uid="{53800147-DB60-4841-9D4F-16EEA6AFCEC2}"/>
-    <hyperlink ref="Q41" r:id="rId37" xr:uid="{261D903B-6D6C-4255-B2EB-D6C458760ED6}"/>
-    <hyperlink ref="Q42" r:id="rId38" xr:uid="{176CFF0E-7C99-4934-8A59-A72C880B0499}"/>
-    <hyperlink ref="Q43" r:id="rId39" xr:uid="{52F57B38-A624-4422-8101-5277938001E9}"/>
-    <hyperlink ref="Q44" r:id="rId40" xr:uid="{22435A1F-6C7C-4F7B-887A-8F95CC844F65}"/>
-    <hyperlink ref="Q45" r:id="rId41" xr:uid="{2313E494-F71A-4817-82A8-04C2FC23FCD3}"/>
-    <hyperlink ref="Q46" r:id="rId42" xr:uid="{4FCC4804-3C51-4D5E-89E7-2CEEC4AEBDDF}"/>
-    <hyperlink ref="Q47" r:id="rId43" display="https://www.worldbank.org/content/dam/Worldbank/document/SAR/nepal/PDNA Volume A Final.pdf" xr:uid="{C16A0E7A-1F81-4F99-B0EB-24B0882E40B9}"/>
-    <hyperlink ref="Q48" r:id="rId44" xr:uid="{9D99DBDD-221C-49D4-9E55-7F20A3F2A7B1}"/>
-    <hyperlink ref="Q49" r:id="rId45" xr:uid="{DA41B2EB-C303-4E89-9D96-D443C427CC80}"/>
-    <hyperlink ref="Q50" r:id="rId46" xr:uid="{17D3D12D-3FE6-47B5-8863-F19B0E70BFC2}"/>
-    <hyperlink ref="Q51" r:id="rId47" xr:uid="{2DD8EAB9-0A02-4443-88A9-6394486EBC01}"/>
-    <hyperlink ref="Q52" r:id="rId48" xr:uid="{5B22EAA0-11FD-4DBF-9966-F599E9BD9FF1}"/>
-    <hyperlink ref="Q53" r:id="rId49" xr:uid="{3060A677-8AE4-48DD-9BF0-3F610F4A6F47}"/>
-    <hyperlink ref="Q54" r:id="rId50" xr:uid="{7D06B00E-D802-4CD9-A448-42825547189C}"/>
-    <hyperlink ref="Q55" r:id="rId51" xr:uid="{7797E73C-2D85-43B2-90CA-CDD133D18BA3}"/>
-    <hyperlink ref="Q56" r:id="rId52" xr:uid="{B8ABE114-85AD-4296-8D19-908827AA0DB5}"/>
-    <hyperlink ref="Q57" r:id="rId53" xr:uid="{71205EE2-33F4-4788-B16A-184BAFEB912D}"/>
-    <hyperlink ref="Q58" r:id="rId54" xr:uid="{645C3A94-8B94-40AD-A4EF-12B76EDAC785}"/>
-    <hyperlink ref="Q59" r:id="rId55" xr:uid="{D72A247F-5B19-4F2C-AF3A-D7EE211C8BD1}"/>
+    <hyperlink ref="Q5" r:id="rId1" xr:uid="{E332A7CA-8377-49C0-9C25-0189B00C1053}"/>
+    <hyperlink ref="Q6" r:id="rId2" xr:uid="{3988F504-D467-46CD-A11C-81DCFD416C93}"/>
+    <hyperlink ref="Q7" r:id="rId3" xr:uid="{FE558717-8F0D-4BD3-A8A6-438FD115570E}"/>
+    <hyperlink ref="Q8" r:id="rId4" xr:uid="{02EA3874-9FB0-4053-A49E-2B7686DA25BA}"/>
+    <hyperlink ref="Q9" r:id="rId5" xr:uid="{478D41B7-A146-47C3-9F90-E819DB812D9B}"/>
+    <hyperlink ref="Q10" r:id="rId6" xr:uid="{D242D625-F674-4433-B679-C674B902F086}"/>
+    <hyperlink ref="Q11" r:id="rId7" xr:uid="{E2A862F8-A9D8-4F0C-9959-5B48D865B2B2}"/>
+    <hyperlink ref="Q12" r:id="rId8" xr:uid="{FF9B0518-5030-4DBE-8340-F903EA3825F1}"/>
+    <hyperlink ref="Q13" r:id="rId9" xr:uid="{597247FB-B1C4-4B57-9B90-ECFE9B4F37D0}"/>
+    <hyperlink ref="Q14" r:id="rId10" xr:uid="{1AC918F8-4738-46EF-BE51-06D8DF1BDA38}"/>
+    <hyperlink ref="Q15" r:id="rId11" xr:uid="{F699BE8D-8118-4DF7-97BE-2932F4033CBA}"/>
+    <hyperlink ref="Q16" r:id="rId12" xr:uid="{CE4D79EE-A96F-46C9-81B5-308F7AA2E5D7}"/>
+    <hyperlink ref="Q17" r:id="rId13" xr:uid="{64DC71FC-8AA7-4427-818C-455C5A2E79DB}"/>
+    <hyperlink ref="Q18" r:id="rId14" xr:uid="{01DA779C-10C7-4FE4-834A-4F60D31D9CF8}"/>
+    <hyperlink ref="Q19" r:id="rId15" xr:uid="{654DD35A-0D3D-495B-A172-8816B56A9D06}"/>
+    <hyperlink ref="Q20" r:id="rId16" xr:uid="{F90B0902-D42E-4FD1-8450-A30A7ADEA71F}"/>
+    <hyperlink ref="Q21" r:id="rId17" xr:uid="{026B03DB-A62D-4E6C-AAEE-8282ACB3F354}"/>
+    <hyperlink ref="Q22" r:id="rId18" xr:uid="{1D9F593C-3533-4A35-B922-7F7EE8218826}"/>
+    <hyperlink ref="Q23" r:id="rId19" xr:uid="{07A389F1-859C-45DC-A6A2-E2E7995D3597}"/>
+    <hyperlink ref="Q24" r:id="rId20" xr:uid="{1EBE2D98-6084-4DC2-9C39-E7E843EC7B2F}"/>
+    <hyperlink ref="Q25" r:id="rId21" xr:uid="{170691B6-214B-49C8-9C25-A32D4FC4E752}"/>
+    <hyperlink ref="Q26" r:id="rId22" xr:uid="{CBB01DC0-3A52-4761-AB8F-DA021835CD6E}"/>
+    <hyperlink ref="Q27" r:id="rId23" xr:uid="{CE1FD3B9-A03F-46E8-AF05-178C117EC6C4}"/>
+    <hyperlink ref="Q28" r:id="rId24" xr:uid="{37A76501-B89D-4BF4-9666-AFE020F372A8}"/>
+    <hyperlink ref="Q29" r:id="rId25" xr:uid="{3F964381-CBDF-454C-A952-108AAA2E79AA}"/>
+    <hyperlink ref="Q30" r:id="rId26" xr:uid="{B44C15F2-3CA0-43EC-9C11-071AE812A66F}"/>
+    <hyperlink ref="Q31" r:id="rId27" xr:uid="{4732E84A-CB76-4A28-949A-DF3D1E848AD3}"/>
+    <hyperlink ref="Q32" r:id="rId28" xr:uid="{5280CF03-6E33-4808-93DE-3B9D46D88445}"/>
+    <hyperlink ref="Q33" r:id="rId29" xr:uid="{25D74DA3-1013-4604-A2BB-0EEF6D6030CE}"/>
+    <hyperlink ref="Q34" r:id="rId30" xr:uid="{6D34BEA6-9660-460A-8117-C220A3F6AF88}"/>
+    <hyperlink ref="Q35" r:id="rId31" xr:uid="{18EDF4FF-C76A-49AE-A6E9-20A356E58496}"/>
+    <hyperlink ref="Q36" r:id="rId32" xr:uid="{57207A0D-1371-435D-8AAA-2E43D7583885}"/>
+    <hyperlink ref="Q37" r:id="rId33" xr:uid="{40468AF2-13B0-41C1-A68F-F56E9DC5A99B}"/>
+    <hyperlink ref="Q38" r:id="rId34" xr:uid="{98790E20-AEA4-4E33-BE62-559BF329DB9A}"/>
+    <hyperlink ref="Q39" r:id="rId35" xr:uid="{D0287478-35D4-4491-90A9-EF8D074A8357}"/>
+    <hyperlink ref="Q40" r:id="rId36" xr:uid="{FF04C289-21B3-4051-BFD1-44FEB1032205}"/>
+    <hyperlink ref="Q41" r:id="rId37" xr:uid="{96E29F09-4641-4A21-B86D-C12EAECFAE1E}"/>
+    <hyperlink ref="Q42" r:id="rId38" xr:uid="{D56E4E47-806A-42E7-839E-F758CCBE5372}"/>
+    <hyperlink ref="Q43" r:id="rId39" xr:uid="{BEFCD012-1EB7-4D11-BEFD-6F6211E395A9}"/>
+    <hyperlink ref="Q44" r:id="rId40" xr:uid="{341C7894-41A2-451E-8F9F-4DE102F2A2A3}"/>
+    <hyperlink ref="Q45" r:id="rId41" xr:uid="{E70A513B-DE08-408F-894A-9A51D4BF591B}"/>
+    <hyperlink ref="Q46" r:id="rId42" xr:uid="{58D627C4-9B81-4EB9-9BD8-73CED98D9650}"/>
+    <hyperlink ref="Q47" r:id="rId43" display="https://www.worldbank.org/content/dam/Worldbank/document/SAR/nepal/PDNA Volume A Final.pdf" xr:uid="{1DE1A4AC-9D98-4FFE-A8EF-A03086E8395F}"/>
+    <hyperlink ref="Q48" r:id="rId44" xr:uid="{0658293C-0B04-4877-B034-86D15DB59E42}"/>
+    <hyperlink ref="Q49" r:id="rId45" xr:uid="{B14CABB4-C8C5-4B4A-BD5A-953C9E05B4F9}"/>
+    <hyperlink ref="Q50" r:id="rId46" xr:uid="{A27E0317-FB5E-45FA-9840-6FC526F8A457}"/>
+    <hyperlink ref="Q51" r:id="rId47" xr:uid="{A3BF5CE6-4D3C-446D-B4EB-D105B51176A3}"/>
+    <hyperlink ref="Q52" r:id="rId48" xr:uid="{C496B14D-10F4-4FB6-8E72-FAE9834258D3}"/>
+    <hyperlink ref="Q53" r:id="rId49" xr:uid="{9D6BAF07-3F46-4397-94E8-465C88CD3392}"/>
+    <hyperlink ref="Q54" r:id="rId50" xr:uid="{3D5D4A56-BF79-46D1-967F-1282A7C3E881}"/>
+    <hyperlink ref="Q55" r:id="rId51" xr:uid="{9F4B601F-CCE1-44ED-9048-92A4D5B3C878}"/>
+    <hyperlink ref="Q56" r:id="rId52" xr:uid="{FD23A468-18DD-4617-99F3-CAE2372CF429}"/>
+    <hyperlink ref="Q57" r:id="rId53" xr:uid="{0D22E96D-4247-48D4-853F-33F5F8E27B35}"/>
+    <hyperlink ref="Q58" r:id="rId54" xr:uid="{F4841326-820C-4562-99D1-E4FD946C8630}"/>
+    <hyperlink ref="Q59" r:id="rId55" xr:uid="{0FD0335A-E32C-487E-9A52-5C608ACF71BA}"/>
+    <hyperlink ref="Q60" r:id="rId56" xr:uid="{94AB0FB5-230F-4B2F-8392-A5A577AC6B53}"/>
+    <hyperlink ref="Q61" r:id="rId57" xr:uid="{AF806AA8-962B-4D93-A8E1-0F5A2DDD694E}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3888888888888889" bottom="0.3888888888888889" header="0.3" footer="0.19444444444444445"/>
-  <pageSetup paperSize="9" scale="29" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId56"/>
+  <pageSetup paperSize="9" scale="29" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId58"/>
   <headerFooter>
     <oddFooter>&amp;CWorking draft | Evidence cutoff 31 July 2026 | Page &amp;P of &amp;N_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 INTERNAL. This information is accessible to ADB Management and Staff. It may be shared outside ADB with appropriate permission.</oddFooter>
   </headerFooter>
   <tableParts count="1">
-    <tablePart r:id="rId57"/>
+    <tablePart r:id="rId59"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28C9A9B8-6AB5-4D30-BC1B-BE4C8FDCB383}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA72C9E7-3E64-43E9-A935-012C0E48A482}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8294,7 +8488,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>782</v>
+        <v>808</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8306,7 +8500,7 @@
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>783</v>
+        <v>809</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8333,13 +8527,13 @@
         <v>55</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>784</v>
+        <v>810</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>785</v>
+        <v>811</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
@@ -8750,21 +8944,21 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H5" r:id="rId1" xr:uid="{BD63353B-40B2-43F0-AE91-839DA09EDA73}"/>
-    <hyperlink ref="H6" r:id="rId2" xr:uid="{D169EFD4-A307-4EBD-A72C-B1C0394EC177}"/>
-    <hyperlink ref="H7" r:id="rId3" xr:uid="{09009A9C-E20D-4E35-AC7B-623D459F132F}"/>
-    <hyperlink ref="H8" r:id="rId4" xr:uid="{8F1B8076-97D6-4167-8C0E-620703A4BE12}"/>
-    <hyperlink ref="H9" r:id="rId5" xr:uid="{FE64AB5F-CA3C-4987-846D-74B626EE05D6}"/>
-    <hyperlink ref="H10" r:id="rId6" xr:uid="{BEDEC184-4568-4FD5-AD7D-0FACC89200C6}"/>
-    <hyperlink ref="H11" r:id="rId7" xr:uid="{5DE08377-168C-41C9-A188-D9210224D9F8}"/>
-    <hyperlink ref="H12" r:id="rId8" xr:uid="{386D7304-9E30-4F95-95EA-0FEC3D7BB713}"/>
-    <hyperlink ref="H13" r:id="rId9" xr:uid="{4285921B-D0C2-4411-A65F-C34880BFED43}"/>
-    <hyperlink ref="H14" r:id="rId10" xr:uid="{5D29F03B-46E7-4B5A-B8A8-3A397160649D}"/>
-    <hyperlink ref="H15" r:id="rId11" xr:uid="{DE82A2F1-3EC2-498F-84A7-93E723616E2C}"/>
-    <hyperlink ref="H16" r:id="rId12" xr:uid="{5EEB6225-CEA0-4DB7-A113-27C43C163392}"/>
-    <hyperlink ref="H17" r:id="rId13" xr:uid="{43A25F84-30B3-4DDE-AC4F-DB59E84CCC22}"/>
-    <hyperlink ref="H18" r:id="rId14" xr:uid="{3794126C-6142-400A-9245-A649E34A74F1}"/>
-    <hyperlink ref="H19" r:id="rId15" xr:uid="{94325608-B1BE-45D7-874B-C607FE9AB801}"/>
+    <hyperlink ref="H5" r:id="rId1" xr:uid="{D3820DF9-3A7E-4523-B38C-CF85E97C1A7E}"/>
+    <hyperlink ref="H6" r:id="rId2" xr:uid="{D76AF7EA-3753-48E4-8923-78D999D1433F}"/>
+    <hyperlink ref="H7" r:id="rId3" xr:uid="{B34915F1-1FE0-4A1C-A5F5-FCB479AF2360}"/>
+    <hyperlink ref="H8" r:id="rId4" xr:uid="{EAADE795-901F-4FA5-8015-5345790BDFD9}"/>
+    <hyperlink ref="H9" r:id="rId5" xr:uid="{C6B6062E-3B69-418F-8B8F-0D4950E35BEC}"/>
+    <hyperlink ref="H10" r:id="rId6" xr:uid="{0482EA20-C067-44A6-BAC4-B1F8182AB8B0}"/>
+    <hyperlink ref="H11" r:id="rId7" xr:uid="{A1F48965-53EA-4CC6-84A3-1D92EDAF55EE}"/>
+    <hyperlink ref="H12" r:id="rId8" xr:uid="{C9C6A60F-8B9B-4647-A67F-85E3CD68F5CA}"/>
+    <hyperlink ref="H13" r:id="rId9" xr:uid="{02EC436A-C4AC-4829-BD4F-09FF8D437C19}"/>
+    <hyperlink ref="H14" r:id="rId10" xr:uid="{4F3E321C-6C47-4390-A670-AE74324122F1}"/>
+    <hyperlink ref="H15" r:id="rId11" xr:uid="{794F4B06-FABC-4120-AB85-B49A9088E93A}"/>
+    <hyperlink ref="H16" r:id="rId12" xr:uid="{D2EE6B04-0090-4AEF-990A-FC0B022A78A8}"/>
+    <hyperlink ref="H17" r:id="rId13" xr:uid="{D9887DCF-2BC5-433B-B630-B4AD7E94E752}"/>
+    <hyperlink ref="H18" r:id="rId14" xr:uid="{A9DDB480-71A2-4175-B9D8-3622AEEE8375}"/>
+    <hyperlink ref="H19" r:id="rId15" xr:uid="{8416C9AD-86B2-4E69-94B7-0383C160CB94}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3888888888888889" bottom="0.3888888888888889" header="0.3" footer="0.19444444444444445"/>
@@ -8776,7 +8970,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB75753C-BB93-4A95-8361-DE1055931DBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38509D58-34CA-4CD7-87CE-7145C0785532}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8794,7 +8988,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>786</v>
+        <v>812</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8804,7 +8998,7 @@
     </row>
     <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>787</v>
+        <v>813</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8814,22 +9008,22 @@
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>788</v>
+        <v>814</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>789</v>
+        <v>815</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>790</v>
+        <v>816</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>791</v>
+        <v>817</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>792</v>
+        <v>818</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8837,19 +9031,19 @@
         <v>254</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>793</v>
+        <v>819</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>794</v>
+        <v>820</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>795</v>
+        <v>821</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>796</v>
+        <v>822</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>797</v>
+        <v>823</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8857,19 +9051,19 @@
         <v>75</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>798</v>
+        <v>824</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>799</v>
+        <v>825</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>800</v>
+        <v>826</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>801</v>
+        <v>827</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>802</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8877,19 +9071,19 @@
         <v>384</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>803</v>
+        <v>829</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>804</v>
+        <v>830</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>805</v>
+        <v>831</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>806</v>
+        <v>832</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>807</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -8907,7 +9101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C47CA43B-4756-4893-943B-1D3896372213}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E145A90-6293-4149-A4A5-5C840181E527}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8922,7 +9116,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>808</v>
+        <v>834</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8934,7 +9128,7 @@
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>809</v>
+        <v>835</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8946,259 +9140,259 @@
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="26" t="s">
-        <v>810</v>
+        <v>836</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>811</v>
+        <v>837</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>812</v>
+        <v>838</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>813</v>
+        <v>839</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="27" t="s">
-        <v>814</v>
+        <v>840</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>815</v>
+        <v>841</v>
       </c>
       <c r="C5" s="28">
         <v>2</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>816</v>
+        <v>842</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="27" t="s">
-        <v>814</v>
+        <v>840</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>817</v>
+        <v>843</v>
       </c>
       <c r="C6" s="28">
         <v>7.75</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>818</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="27" t="s">
-        <v>814</v>
+        <v>840</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>819</v>
+        <v>845</v>
       </c>
       <c r="C7" s="28">
         <v>11</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>816</v>
+        <v>842</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="27" t="s">
-        <v>814</v>
+        <v>840</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>820</v>
+        <v>846</v>
       </c>
       <c r="C8" s="28">
         <v>11.9</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>821</v>
+        <v>847</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="27" t="s">
-        <v>822</v>
+        <v>848</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>823</v>
+        <v>849</v>
       </c>
       <c r="C9" s="28">
         <v>81</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>824</v>
+        <v>850</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="27" t="s">
-        <v>822</v>
+        <v>848</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>825</v>
+        <v>851</v>
       </c>
       <c r="C10" s="28">
         <v>77.5</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>826</v>
+        <v>852</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="27" t="s">
-        <v>822</v>
+        <v>848</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>827</v>
+        <v>853</v>
       </c>
       <c r="C11" s="28">
         <v>8.75</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>826</v>
+        <v>852</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="27" t="s">
-        <v>822</v>
+        <v>848</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>828</v>
+        <v>854</v>
       </c>
       <c r="C12" s="28">
         <v>4.07</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>829</v>
+        <v>855</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="27" t="s">
-        <v>830</v>
+        <v>856</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>831</v>
+        <v>857</v>
       </c>
       <c r="C13" s="28">
         <v>3.8</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>816</v>
+        <v>842</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
-        <v>830</v>
+        <v>856</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>832</v>
+        <v>858</v>
       </c>
       <c r="C14" s="28">
         <v>14.4</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>816</v>
+        <v>842</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="27" t="s">
-        <v>830</v>
+        <v>856</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>833</v>
+        <v>859</v>
       </c>
       <c r="C15" s="28">
         <v>18</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>821</v>
+        <v>847</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="27" t="s">
-        <v>830</v>
+        <v>856</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>834</v>
+        <v>860</v>
       </c>
       <c r="C16" s="28">
         <v>9</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>835</v>
+        <v>861</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="27" t="s">
-        <v>836</v>
+        <v>862</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>837</v>
+        <v>863</v>
       </c>
       <c r="C17" s="28">
         <v>18.5</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>838</v>
+        <v>864</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="27" t="s">
-        <v>836</v>
+        <v>862</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>839</v>
+        <v>865</v>
       </c>
       <c r="C18" s="28">
         <v>31</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>838</v>
+        <v>864</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="27" t="s">
-        <v>836</v>
+        <v>862</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>840</v>
+        <v>866</v>
       </c>
       <c r="C19" s="28">
         <v>64</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>838</v>
+        <v>864</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="27" t="s">
-        <v>836</v>
+        <v>862</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>841</v>
+        <v>867</v>
       </c>
       <c r="C20" s="28">
         <v>41</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>842</v>
+        <v>868</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>843</v>
+        <v>869</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>844</v>
+        <v>870</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>845</v>
+        <v>871</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>846</v>
+        <v>872</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>847</v>
+        <v>873</v>
       </c>
       <c r="B24" s="5">
         <v>1</v>
@@ -9212,7 +9406,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>848</v>
+        <v>874</v>
       </c>
       <c r="B25" s="5">
         <v>2</v>
@@ -9226,7 +9420,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
       <c r="B26" s="5">
         <v>3</v>
@@ -9240,7 +9434,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>850</v>
+        <v>876</v>
       </c>
       <c r="B27" s="5">
         <v>3</v>
@@ -9254,7 +9448,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>851</v>
+        <v>877</v>
       </c>
       <c r="B28" s="5">
         <v>2</v>
@@ -9268,7 +9462,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>852</v>
+        <v>878</v>
       </c>
       <c r="B29" s="5">
         <v>2</v>
@@ -9282,7 +9476,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="29" t="s">
-        <v>853</v>
+        <v>879</v>
       </c>
       <c r="B30" s="5">
         <v>3</v>
@@ -9296,10 +9490,10 @@
     </row>
     <row r="34" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>854</v>
+        <v>880</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>855</v>
+        <v>881</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -9328,10 +9522,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>856</v>
+        <v>882</v>
       </c>
       <c r="B38" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -9357,7 +9551,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50E6C523-A4B2-46E2-B078-F2D6F5A25AA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133391F2-1698-4F17-9013-D96FDCBB938A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -9374,7 +9568,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9383,7 +9577,7 @@
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>858</v>
+        <v>884</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9392,104 +9586,104 @@
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>859</v>
+        <v>885</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>860</v>
+        <v>886</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>861</v>
+        <v>887</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>862</v>
+        <v>888</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>863</v>
+        <v>889</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>865</v>
+        <v>891</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>866</v>
+        <v>892</v>
       </c>
       <c r="D5" s="8">
         <v>46238</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>867</v>
+        <v>893</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>868</v>
+        <v>894</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>869</v>
+        <v>895</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>870</v>
+        <v>896</v>
       </c>
       <c r="D6" s="8">
         <v>46238</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>871</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>872</v>
+        <v>898</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>873</v>
+        <v>899</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>874</v>
+        <v>900</v>
       </c>
       <c r="D7" s="8">
         <v>46238</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>875</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>876</v>
+        <v>902</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>877</v>
+        <v>903</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>878</v>
+        <v>904</v>
       </c>
       <c r="D8" s="8">
         <v>46238</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>879</v>
+        <v>905</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>880</v>
+        <v>906</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>881</v>
+        <v>907</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>882</v>
+        <v>908</v>
       </c>
       <c r="D9" s="8">
         <v>46238</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>883</v>
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -9507,11 +9701,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7607B8A-B629-46C6-9792-1315A0B23624}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0051ECD1-0B49-4628-96D1-882E9C2495FB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
@@ -9522,27 +9716,27 @@
   <sheetData>
     <row r="1" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>884</v>
+        <v>910</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>885</v>
+        <v>911</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>886</v>
+        <v>912</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>887</v>
+        <v>913</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>888</v>
+        <v>914</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9550,10 +9744,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>889</v>
+        <v>915</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9561,10 +9755,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>891</v>
+        <v>917</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9572,10 +9766,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>892</v>
+        <v>918</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9583,10 +9777,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>893</v>
+        <v>919</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9594,10 +9788,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>894</v>
+        <v>920</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9605,10 +9799,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>895</v>
+        <v>921</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9616,10 +9810,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>896</v>
+        <v>922</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9627,10 +9821,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>897</v>
+        <v>923</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9638,10 +9832,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>898</v>
+        <v>924</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9649,10 +9843,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>899</v>
+        <v>925</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9660,10 +9854,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>900</v>
+        <v>926</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9671,10 +9865,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>901</v>
+        <v>927</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9682,10 +9876,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>902</v>
+        <v>928</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9693,10 +9887,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>903</v>
+        <v>929</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9704,10 +9898,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>904</v>
+        <v>930</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9715,10 +9909,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>905</v>
+        <v>931</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9726,10 +9920,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>906</v>
+        <v>932</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9737,10 +9931,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>907</v>
+        <v>933</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9748,10 +9942,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>908</v>
+        <v>934</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9759,10 +9953,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9770,10 +9964,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>910</v>
+        <v>936</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9781,10 +9975,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>911</v>
+        <v>937</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9792,10 +9986,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>912</v>
+        <v>938</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9803,10 +9997,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>913</v>
+        <v>939</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9814,10 +10008,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>914</v>
+        <v>940</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9825,10 +10019,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>915</v>
+        <v>941</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9836,10 +10030,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>942</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>916</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9847,10 +10041,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>917</v>
+        <v>943</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9858,10 +10052,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>918</v>
+        <v>944</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9869,10 +10063,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>919</v>
+        <v>945</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9880,10 +10074,10 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>920</v>
+        <v>946</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9891,10 +10085,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>921</v>
+        <v>947</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9902,10 +10096,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>922</v>
+        <v>948</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9913,10 +10107,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>923</v>
+        <v>949</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9924,10 +10118,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>924</v>
+        <v>950</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9935,10 +10129,10 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>925</v>
+        <v>951</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9946,10 +10140,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>926</v>
+        <v>952</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9957,10 +10151,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>927</v>
+        <v>953</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9968,10 +10162,10 @@
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>928</v>
+        <v>954</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9979,10 +10173,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>929</v>
+        <v>955</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -9990,10 +10184,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>930</v>
+        <v>956</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10001,10 +10195,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>931</v>
+        <v>957</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10012,10 +10206,10 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>932</v>
+        <v>958</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10023,10 +10217,10 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>933</v>
+        <v>959</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10034,10 +10228,10 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>934</v>
+        <v>960</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10045,10 +10239,10 @@
         <v>46</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>935</v>
+        <v>961</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10056,10 +10250,10 @@
         <v>47</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>936</v>
+        <v>962</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10067,10 +10261,10 @@
         <v>48</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>937</v>
+        <v>963</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10078,10 +10272,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>938</v>
+        <v>964</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10089,10 +10283,10 @@
         <v>50</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>939</v>
+        <v>965</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10100,10 +10294,10 @@
         <v>51</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>940</v>
+        <v>966</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10111,10 +10305,10 @@
         <v>52</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>941</v>
+        <v>967</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10122,10 +10316,10 @@
         <v>53</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>942</v>
+        <v>968</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10133,10 +10327,10 @@
         <v>54</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>943</v>
+        <v>969</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10144,10 +10338,10 @@
         <v>55</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>944</v>
+        <v>970</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10155,10 +10349,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>945</v>
+        <v>971</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -10166,10 +10360,32 @@
         <v>57</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>946</v>
+        <v>972</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>890</v>
+        <v>916</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7">
+        <v>58</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="7">
+        <v>59</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>916</v>
       </c>
     </row>
   </sheetData>
